--- a/dados/excel/quadro_escolaridade_categoria_secretaria.xlsx
+++ b/dados/excel/quadro_escolaridade_categoria_secretaria.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$F$401</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$F$402</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10">
@@ -633,7 +633,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F401"/>
+  <dimension ref="A1:F402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -968,13 +968,13 @@
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7" s="14" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>537291.54</v>
+        <v>554909.34</v>
       </c>
     </row>
     <row r="8">
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>147617.25</v>
+        <v>162343.79</v>
       </c>
     </row>
     <row r="9">
@@ -1046,13 +1046,13 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>6</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>1655727.78</v>
+        <v>1707827.91</v>
       </c>
     </row>
     <row r="11">
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>1467033.8</v>
+        <v>1501908.08</v>
       </c>
     </row>
     <row r="12">
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>2</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>869525.61</v>
+        <v>898429.7</v>
       </c>
     </row>
     <row r="13">
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>3</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>217275.28</v>
+        <v>234576.65</v>
       </c>
     </row>
     <row r="15">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>15</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>1902756.08</v>
+        <v>1937473.15</v>
       </c>
     </row>
     <row r="17">
@@ -1228,13 +1228,13 @@
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>2573</v>
+        <v>2615</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>63</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>9735248.710000001</v>
+        <v>9932508.73</v>
       </c>
     </row>
     <row r="18">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>6297</v>
+        <v>6391</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>171</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>28840696.02</v>
+        <v>29400828.29</v>
       </c>
     </row>
     <row r="19">
@@ -1280,13 +1280,13 @@
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>389229.55</v>
+        <v>396512.23</v>
       </c>
     </row>
     <row r="20">
@@ -1306,13 +1306,13 @@
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>917</v>
+        <v>933</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>20</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>6757702.98</v>
+        <v>6895644.49</v>
       </c>
     </row>
     <row r="21">
@@ -1332,13 +1332,13 @@
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>604</v>
+        <v>615</v>
       </c>
       <c r="E21" s="14" t="n">
         <v>17</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>6226381.17</v>
+        <v>6356688.23</v>
       </c>
     </row>
     <row r="22">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>7</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>586298.29</v>
+        <v>592435.74</v>
       </c>
     </row>
     <row r="23">
@@ -1410,13 +1410,13 @@
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>130468.31</v>
+        <v>135449.24</v>
       </c>
     </row>
     <row r="25">
@@ -1436,13 +1436,13 @@
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>2772</v>
+        <v>2833</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>10998463.64</v>
+        <v>11307008.21</v>
       </c>
     </row>
     <row r="26">
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1354717.64</v>
+        <v>1361205.13</v>
       </c>
     </row>
     <row r="27">
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E27" s="14" t="n">
         <v>7</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>751278.03</v>
+        <v>768612.83</v>
       </c>
     </row>
     <row r="28">
@@ -1540,13 +1540,13 @@
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E29" s="14" t="n">
         <v>7</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>920974.54</v>
+        <v>937004.85</v>
       </c>
     </row>
     <row r="30">
@@ -1566,13 +1566,13 @@
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>324609.2</v>
+        <v>333539.16</v>
       </c>
     </row>
     <row r="31">
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>135512.72</v>
+        <v>139593.44</v>
       </c>
     </row>
     <row r="32">
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>7657</v>
+        <v>7798</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>199</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>53319623.7</v>
+        <v>54587352.66</v>
       </c>
     </row>
     <row r="33">
@@ -1644,13 +1644,13 @@
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>2393</v>
+        <v>2429</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>23184903.61</v>
+        <v>23625417.12</v>
       </c>
     </row>
     <row r="34">
@@ -1670,13 +1670,13 @@
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>2031</v>
+        <v>2065</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>52</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>13360089.12</v>
+        <v>13623316.54</v>
       </c>
     </row>
     <row r="35">
@@ -1696,13 +1696,13 @@
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="E35" s="14" t="n">
         <v>37</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>5162785.28</v>
+        <v>5327969.25</v>
       </c>
     </row>
     <row r="36">
@@ -1722,13 +1722,13 @@
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>2061</v>
+        <v>2088</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>37</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>17847594.91</v>
+        <v>18181604.77</v>
       </c>
     </row>
     <row r="37">
@@ -1748,13 +1748,13 @@
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E37" s="14" t="n">
         <v>6</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>2868125.04</v>
+        <v>2925169.77</v>
       </c>
     </row>
     <row r="38">
@@ -1774,13 +1774,13 @@
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>6</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>2211818.05</v>
+        <v>2251562.78</v>
       </c>
     </row>
     <row r="39">
@@ -1800,13 +1800,13 @@
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E39" s="14" t="n">
         <v>4</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>874526.59</v>
+        <v>915616.1899999999</v>
       </c>
     </row>
     <row r="40">
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E41" s="14" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>675653.42</v>
+        <v>690037.75</v>
       </c>
     </row>
     <row r="42">
@@ -1878,13 +1878,13 @@
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>3</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>540074.84</v>
+        <v>546142.88</v>
       </c>
     </row>
     <row r="43">
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="D43" s="14" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E43" s="14" t="n">
         <v>7</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>720852.11</v>
+        <v>725711.76</v>
       </c>
     </row>
     <row r="44">
@@ -1930,13 +1930,13 @@
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>4106</v>
+        <v>4175</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>88</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>12017930.08</v>
+        <v>12318750.25</v>
       </c>
     </row>
     <row r="45">
@@ -1956,13 +1956,13 @@
         </is>
       </c>
       <c r="D45" s="14" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>811972.98</v>
+        <v>813762.42</v>
       </c>
     </row>
     <row r="46">
@@ -1982,13 +1982,13 @@
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>5</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>1202521.61</v>
+        <v>1239419.76</v>
       </c>
     </row>
     <row r="47">
@@ -2034,13 +2034,13 @@
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>85557</v>
+        <v>86952</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>1831</v>
+        <v>1859</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>290089431.06</v>
+        <v>296514547.14</v>
       </c>
     </row>
     <row r="49">
@@ -2060,13 +2060,13 @@
         </is>
       </c>
       <c r="D49" s="14" t="n">
-        <v>7973</v>
+        <v>8085</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>809</v>
+        <v>827</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>16837859.4</v>
+        <v>17090697.39</v>
       </c>
     </row>
     <row r="50">
@@ -2086,13 +2086,13 @@
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>3</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>438974.08</v>
+        <v>478079.98</v>
       </c>
     </row>
     <row r="51">
@@ -2138,13 +2138,13 @@
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>38076</v>
+        <v>38620</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>3217</v>
+        <v>3252</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>44471294.24</v>
+        <v>45392002.2</v>
       </c>
     </row>
     <row r="53">
@@ -2164,13 +2164,13 @@
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>5651</v>
+        <v>5730</v>
       </c>
       <c r="E53" s="14" t="n">
         <v>102</v>
       </c>
       <c r="F53" s="15" t="n">
-        <v>22362615.95</v>
+        <v>22826717.23</v>
       </c>
     </row>
     <row r="54">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="D55" s="14" t="n">
-        <v>154761</v>
+        <v>157585</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>3831</v>
+        <v>3929</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>1016671441.93</v>
+        <v>1042409815.26</v>
       </c>
     </row>
     <row r="56">
@@ -2242,13 +2242,13 @@
         </is>
       </c>
       <c r="D56" s="10" t="n">
-        <v>79133</v>
+        <v>81320</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>5540</v>
+        <v>5701</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>120312727.53</v>
+        <v>124960244.72</v>
       </c>
     </row>
     <row r="57">
@@ -2268,13 +2268,13 @@
         </is>
       </c>
       <c r="D57" s="14" t="n">
-        <v>2580</v>
+        <v>2622</v>
       </c>
       <c r="E57" s="14" t="n">
         <v>74</v>
       </c>
       <c r="F57" s="15" t="n">
-        <v>28300209.27</v>
+        <v>28924471.94</v>
       </c>
     </row>
     <row r="58">
@@ -2294,13 +2294,13 @@
         </is>
       </c>
       <c r="D58" s="10" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>19</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2802360.23</v>
+        <v>2873528.53</v>
       </c>
     </row>
     <row r="59">
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="D59" s="14" t="n">
-        <v>96495</v>
+        <v>97828</v>
       </c>
       <c r="E59" s="14" t="n">
         <v>1629</v>
       </c>
       <c r="F59" s="15" t="n">
-        <v>1026627421.08</v>
+        <v>1047755253.04</v>
       </c>
     </row>
     <row r="60">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="D60" s="10" t="n">
-        <v>8029</v>
+        <v>8207</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>9709057.32</v>
+        <v>10008308.08</v>
       </c>
     </row>
     <row r="61">
@@ -2372,13 +2372,13 @@
         </is>
       </c>
       <c r="D61" s="14" t="n">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="E61" s="14" t="n">
         <v>18</v>
       </c>
       <c r="F61" s="15" t="n">
-        <v>7716943.1</v>
+        <v>7841517.02</v>
       </c>
     </row>
     <row r="62">
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="D62" s="10" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E62" s="10" t="n">
         <v>7</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1613202.51</v>
+        <v>1660922.18</v>
       </c>
     </row>
     <row r="63">
@@ -2424,13 +2424,13 @@
         </is>
       </c>
       <c r="D63" s="14" t="n">
-        <v>4527</v>
+        <v>4593</v>
       </c>
       <c r="E63" s="14" t="n">
         <v>73</v>
       </c>
       <c r="F63" s="15" t="n">
-        <v>63511328.2</v>
+        <v>64840209.03</v>
       </c>
     </row>
     <row r="64">
@@ -2502,13 +2502,13 @@
         </is>
       </c>
       <c r="D66" s="10" t="n">
-        <v>821</v>
+        <v>831</v>
       </c>
       <c r="E66" s="10" t="n">
         <v>13</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>11012385.13</v>
+        <v>11206973.19</v>
       </c>
     </row>
     <row r="67">
@@ -2554,13 +2554,13 @@
         </is>
       </c>
       <c r="D68" s="10" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E68" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>213700.95</v>
+        <v>217504.59</v>
       </c>
     </row>
     <row r="69">
@@ -2632,13 +2632,13 @@
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>2086</v>
+        <v>2123</v>
       </c>
       <c r="E71" s="14" t="n">
         <v>55</v>
       </c>
       <c r="F71" s="15" t="n">
-        <v>8089768.11</v>
+        <v>8340358.93</v>
       </c>
     </row>
     <row r="72">
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="D72" s="10" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E72" s="10" t="n">
         <v>2</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>417496.13</v>
+        <v>445046.31</v>
       </c>
     </row>
     <row r="73">
@@ -2710,13 +2710,13 @@
         </is>
       </c>
       <c r="D74" s="10" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E74" s="10" t="n">
         <v>7</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>793151.65</v>
+        <v>810554.5</v>
       </c>
     </row>
     <row r="75">
@@ -2736,13 +2736,13 @@
         </is>
       </c>
       <c r="D75" s="14" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E75" s="14" t="n">
         <v>29</v>
       </c>
       <c r="F75" s="15" t="n">
-        <v>266657.12</v>
+        <v>267594.88</v>
       </c>
     </row>
     <row r="76">
@@ -2762,13 +2762,13 @@
         </is>
       </c>
       <c r="D76" s="10" t="n">
-        <v>6202</v>
+        <v>6281</v>
       </c>
       <c r="E76" s="10" t="n">
         <v>125</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>55956244.54</v>
+        <v>57175862.97</v>
       </c>
     </row>
     <row r="77">
@@ -2788,13 +2788,13 @@
         </is>
       </c>
       <c r="D77" s="14" t="n">
-        <v>2395</v>
+        <v>2429</v>
       </c>
       <c r="E77" s="14" t="n">
         <v>54</v>
       </c>
       <c r="F77" s="15" t="n">
-        <v>25212618.46</v>
+        <v>25718907.2</v>
       </c>
     </row>
     <row r="78">
@@ -2814,13 +2814,13 @@
         </is>
       </c>
       <c r="D78" s="10" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E78" s="10" t="n">
         <v>13</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1160693.8</v>
+        <v>1213766.22</v>
       </c>
     </row>
     <row r="79">
@@ -2866,13 +2866,13 @@
         </is>
       </c>
       <c r="D80" s="10" t="n">
-        <v>1078</v>
+        <v>1093</v>
       </c>
       <c r="E80" s="10" t="n">
         <v>20</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>15194250.52</v>
+        <v>15516559.7</v>
       </c>
     </row>
     <row r="81">
@@ -2892,13 +2892,13 @@
         </is>
       </c>
       <c r="D81" s="14" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E81" s="14" t="n">
         <v>2</v>
       </c>
       <c r="F81" s="15" t="n">
-        <v>1643360.44</v>
+        <v>1699188.18</v>
       </c>
     </row>
     <row r="82">
@@ -2944,13 +2944,13 @@
         </is>
       </c>
       <c r="D83" s="14" t="n">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="E83" s="14" t="n">
         <v>14</v>
       </c>
       <c r="F83" s="15" t="n">
-        <v>1469485.2</v>
+        <v>1506221.64</v>
       </c>
     </row>
     <row r="84">
@@ -3048,13 +3048,13 @@
         </is>
       </c>
       <c r="D87" s="14" t="n">
-        <v>1025</v>
+        <v>1043</v>
       </c>
       <c r="E87" s="14" t="n">
         <v>26</v>
       </c>
       <c r="F87" s="15" t="n">
-        <v>8658093.16</v>
+        <v>8854485.960000001</v>
       </c>
     </row>
     <row r="88">
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="D88" s="10" t="n">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="E88" s="10" t="n">
         <v>16</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>4590336.49</v>
+        <v>4703461.02</v>
       </c>
     </row>
     <row r="89">
@@ -3100,13 +3100,13 @@
         </is>
       </c>
       <c r="D89" s="14" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E89" s="14" t="n">
         <v>15</v>
       </c>
       <c r="F89" s="15" t="n">
-        <v>2401599.62</v>
+        <v>2455002.28</v>
       </c>
     </row>
     <row r="90">
@@ -3126,13 +3126,13 @@
         </is>
       </c>
       <c r="D90" s="10" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E90" s="10" t="n">
         <v>3</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1723654.12</v>
+        <v>1778209.93</v>
       </c>
     </row>
     <row r="91">
@@ -3204,13 +3204,13 @@
         </is>
       </c>
       <c r="D93" s="14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E93" s="14" t="n">
         <v>2</v>
       </c>
       <c r="F93" s="15" t="n">
-        <v>233930.11</v>
+        <v>254850.97</v>
       </c>
     </row>
     <row r="94">
@@ -3230,13 +3230,13 @@
         </is>
       </c>
       <c r="D94" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E94" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>111621.06</v>
+        <v>128732.39</v>
       </c>
     </row>
     <row r="95">
@@ -3273,22 +3273,22 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D96" s="10" t="n">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1654073.38</v>
+        <v>1930.24</v>
       </c>
     </row>
     <row r="97">
@@ -3304,17 +3304,17 @@
       </c>
       <c r="C97" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D97" s="14" t="n">
-        <v>42</v>
+        <v>109</v>
       </c>
       <c r="E97" s="14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F97" s="15" t="n">
-        <v>513573.65</v>
+        <v>1761353.97</v>
       </c>
     </row>
     <row r="98">
@@ -3330,17 +3330,17 @@
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D98" s="10" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E98" s="10" t="n">
         <v>3</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>153468.53</v>
+        <v>529335.74</v>
       </c>
     </row>
     <row r="99">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C99" s="13" t="inlineStr">
@@ -3360,13 +3360,13 @@
         </is>
       </c>
       <c r="D99" s="14" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E99" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F99" s="15" t="n">
-        <v>305332.95</v>
+        <v>158774.75</v>
       </c>
     </row>
     <row r="100">
@@ -3382,17 +3382,17 @@
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D100" s="10" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>158408.1</v>
+        <v>319309.8</v>
       </c>
     </row>
     <row r="101">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="C101" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D101" s="14" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E101" s="14" t="n">
         <v>1</v>
       </c>
       <c r="F101" s="15" t="n">
-        <v>56306.18</v>
+        <v>174200.51</v>
       </c>
     </row>
     <row r="102">
@@ -3429,33 +3429,33 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D102" s="10" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E102" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>646224.5</v>
+        <v>56306.18</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
         <is>
-          <t>Secretaria da Saúde</t>
+          <t>Secretaria da Mulher</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C103" s="13" t="inlineStr">
@@ -3464,13 +3464,13 @@
         </is>
       </c>
       <c r="D103" s="14" t="n">
-        <v>607</v>
+        <v>18</v>
       </c>
       <c r="E103" s="14" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F103" s="15" t="n">
-        <v>4132265.46</v>
+        <v>646224.5</v>
       </c>
     </row>
     <row r="104">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
@@ -3490,13 +3490,13 @@
         </is>
       </c>
       <c r="D104" s="10" t="n">
-        <v>4223</v>
+        <v>612</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>19125842.32</v>
+        <v>4213516.81</v>
       </c>
     </row>
     <row r="105">
@@ -3512,17 +3512,17 @@
       </c>
       <c r="C105" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D105" s="14" t="n">
-        <v>45</v>
+        <v>4290</v>
       </c>
       <c r="E105" s="14" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="F105" s="15" t="n">
-        <v>179793.3</v>
+        <v>19477081.66</v>
       </c>
     </row>
     <row r="106">
@@ -3533,22 +3533,22 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D106" s="10" t="n">
-        <v>458</v>
+        <v>45</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>2350812.6</v>
+        <v>179793.3</v>
       </c>
     </row>
     <row r="107">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C107" s="13" t="inlineStr">
@@ -3568,13 +3568,13 @@
         </is>
       </c>
       <c r="D107" s="14" t="n">
-        <v>70689</v>
+        <v>464</v>
       </c>
       <c r="E107" s="14" t="n">
-        <v>1574</v>
+        <v>9</v>
       </c>
       <c r="F107" s="15" t="n">
-        <v>376450918.33</v>
+        <v>2395651.26</v>
       </c>
     </row>
     <row r="108">
@@ -3590,17 +3590,17 @@
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D108" s="10" t="n">
-        <v>175</v>
+        <v>72110</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>13</v>
+        <v>1582</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1180090.57</v>
+        <v>385267039.32</v>
       </c>
     </row>
     <row r="109">
@@ -3616,17 +3616,17 @@
       </c>
       <c r="C109" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D109" s="14" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E109" s="14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F109" s="15" t="n">
-        <v>194141.92</v>
+        <v>1252286.47</v>
       </c>
     </row>
     <row r="110">
@@ -3637,22 +3637,22 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D110" s="10" t="n">
-        <v>2885</v>
+        <v>186</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>16638007.82</v>
+        <v>194141.92</v>
       </c>
     </row>
     <row r="111">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="C111" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D111" s="14" t="n">
-        <v>245</v>
+        <v>2929</v>
       </c>
       <c r="E111" s="14" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F111" s="15" t="n">
-        <v>2311006.74</v>
+        <v>16962064.66</v>
       </c>
     </row>
     <row r="112">
@@ -3694,17 +3694,17 @@
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D112" s="10" t="n">
-        <v>2007</v>
+        <v>246</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>197</v>
+        <v>10</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>2032183.72</v>
+        <v>2325836.92</v>
       </c>
     </row>
     <row r="113">
@@ -3715,22 +3715,22 @@
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C113" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D113" s="14" t="n">
-        <v>63273</v>
+        <v>2048</v>
       </c>
       <c r="E113" s="14" t="n">
-        <v>1367</v>
+        <v>197</v>
       </c>
       <c r="F113" s="15" t="n">
-        <v>698495162.6</v>
+        <v>2074773</v>
       </c>
     </row>
     <row r="114">
@@ -3746,17 +3746,17 @@
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D114" s="10" t="n">
-        <v>7360</v>
+        <v>64382</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>192</v>
+        <v>1370</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>96048566.34999999</v>
+        <v>713343201.21</v>
       </c>
     </row>
     <row r="115">
@@ -3772,17 +3772,17 @@
       </c>
       <c r="C115" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D115" s="14" t="n">
-        <v>1949</v>
+        <v>7468</v>
       </c>
       <c r="E115" s="14" t="n">
-        <v>100</v>
+        <v>192</v>
       </c>
       <c r="F115" s="15" t="n">
-        <v>30182015.33</v>
+        <v>97729579.63</v>
       </c>
     </row>
     <row r="116">
@@ -3798,17 +3798,17 @@
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D116" s="10" t="n">
-        <v>697</v>
+        <v>1949</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>9909818.17</v>
+        <v>30182015.33</v>
       </c>
     </row>
     <row r="117">
@@ -3819,22 +3819,22 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C117" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D117" s="14" t="n">
-        <v>21152</v>
+        <v>715</v>
       </c>
       <c r="E117" s="14" t="n">
-        <v>355</v>
+        <v>60</v>
       </c>
       <c r="F117" s="15" t="n">
-        <v>331733653.86</v>
+        <v>10228386.66</v>
       </c>
     </row>
     <row r="118">
@@ -3850,17 +3850,17 @@
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D118" s="10" t="n">
-        <v>2333</v>
+        <v>21465</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>57</v>
+        <v>355</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>45140932.98</v>
+        <v>337771669.07</v>
       </c>
     </row>
     <row r="119">
@@ -3876,17 +3876,17 @@
       </c>
       <c r="C119" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D119" s="14" t="n">
-        <v>83</v>
+        <v>2366</v>
       </c>
       <c r="E119" s="14" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="F119" s="15" t="n">
-        <v>1359785.32</v>
+        <v>46031829.8</v>
       </c>
     </row>
     <row r="120">
@@ -3902,17 +3902,17 @@
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D120" s="10" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>298949.82</v>
+        <v>1395095.69</v>
       </c>
     </row>
     <row r="121">
@@ -3923,22 +3923,22 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C121" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D121" s="14" t="n">
-        <v>2616</v>
+        <v>34</v>
       </c>
       <c r="E121" s="14" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="F121" s="15" t="n">
-        <v>36097863.21</v>
+        <v>298949.82</v>
       </c>
     </row>
     <row r="122">
@@ -3954,17 +3954,17 @@
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D122" s="10" t="n">
-        <v>258</v>
+        <v>2655</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>7655420.99</v>
+        <v>36902908.17</v>
       </c>
     </row>
     <row r="123">
@@ -3980,17 +3980,17 @@
       </c>
       <c r="C123" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>7</v>
+        <v>263</v>
       </c>
       <c r="E123" s="14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F123" s="15" t="n">
-        <v>107928.88</v>
+        <v>7837546.37</v>
       </c>
     </row>
     <row r="124">
@@ -4001,22 +4001,22 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>Doutorado</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D124" s="10" t="n">
-        <v>1108</v>
+        <v>7</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>17441133.8</v>
+        <v>107928.88</v>
       </c>
     </row>
     <row r="125">
@@ -4032,43 +4032,43 @@
       </c>
       <c r="C125" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D125" s="14" t="n">
-        <v>74</v>
+        <v>1125</v>
       </c>
       <c r="E125" s="14" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F125" s="15" t="n">
-        <v>3086391.56</v>
+        <v>17867974.25</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Administração</t>
+          <t>Secretaria da Saúde</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Doutorado</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D126" s="10" t="n">
-        <v>817</v>
+        <v>74</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>5539826.45</v>
+        <v>3086391.56</v>
       </c>
     </row>
     <row r="127">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C127" s="13" t="inlineStr">
@@ -4088,13 +4088,13 @@
         </is>
       </c>
       <c r="D127" s="14" t="n">
-        <v>612</v>
+        <v>826</v>
       </c>
       <c r="E127" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F127" s="15" t="n">
-        <v>3014308.94</v>
+        <v>5657343.64</v>
       </c>
     </row>
     <row r="128">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
@@ -4114,13 +4114,13 @@
         </is>
       </c>
       <c r="D128" s="10" t="n">
-        <v>244</v>
+        <v>617</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1689825.92</v>
+        <v>3047653.64</v>
       </c>
     </row>
     <row r="129">
@@ -4136,17 +4136,17 @@
       </c>
       <c r="C129" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D129" s="14" t="n">
-        <v>93</v>
+        <v>246</v>
       </c>
       <c r="E129" s="14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F129" s="15" t="n">
-        <v>91640</v>
+        <v>1706524.55</v>
       </c>
     </row>
     <row r="130">
@@ -4157,22 +4157,22 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D130" s="10" t="n">
-        <v>2293</v>
+        <v>93</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>10540838.58</v>
+        <v>91640</v>
       </c>
     </row>
     <row r="131">
@@ -4188,17 +4188,17 @@
       </c>
       <c r="C131" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D131" s="14" t="n">
-        <v>97</v>
+        <v>2327</v>
       </c>
       <c r="E131" s="14" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="F131" s="15" t="n">
-        <v>823598.4399999999</v>
+        <v>10735756.73</v>
       </c>
     </row>
     <row r="132">
@@ -4214,17 +4214,17 @@
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D132" s="10" t="n">
-        <v>228</v>
+        <v>99</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>235438.56</v>
+        <v>838180.66</v>
       </c>
     </row>
     <row r="133">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C133" s="13" t="inlineStr">
@@ -4244,13 +4244,13 @@
         </is>
       </c>
       <c r="D133" s="14" t="n">
-        <v>2060</v>
+        <v>228</v>
       </c>
       <c r="E133" s="14" t="n">
-        <v>195</v>
+        <v>22</v>
       </c>
       <c r="F133" s="15" t="n">
-        <v>2114151.84</v>
+        <v>235438.56</v>
       </c>
     </row>
     <row r="134">
@@ -4266,17 +4266,17 @@
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D134" s="10" t="n">
-        <v>241</v>
+        <v>2077</v>
       </c>
       <c r="E134" s="10" t="n">
-        <v>5</v>
+        <v>195</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1294940.14</v>
+        <v>2132352.96</v>
       </c>
     </row>
     <row r="135">
@@ -4292,17 +4292,17 @@
       </c>
       <c r="C135" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>15</v>
+        <v>244</v>
       </c>
       <c r="E135" s="14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F135" s="15" t="n">
-        <v>105357.67</v>
+        <v>1318984.04</v>
       </c>
     </row>
     <row r="136">
@@ -4313,22 +4313,22 @@
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D136" s="10" t="n">
-        <v>5095</v>
+        <v>15</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>156</v>
+        <v>1</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>35617649.81</v>
+        <v>105357.67</v>
       </c>
     </row>
     <row r="137">
@@ -4344,17 +4344,17 @@
       </c>
       <c r="C137" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D137" s="14" t="n">
-        <v>2988</v>
+        <v>5142</v>
       </c>
       <c r="E137" s="14" t="n">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="F137" s="15" t="n">
-        <v>31175801.32</v>
+        <v>36052579.27</v>
       </c>
     </row>
     <row r="138">
@@ -4370,17 +4370,17 @@
       </c>
       <c r="C138" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D138" s="10" t="n">
-        <v>267</v>
+        <v>3025</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>4050144.48</v>
+        <v>31754512.03</v>
       </c>
     </row>
     <row r="139">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="C139" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
-        <v>29</v>
+        <v>269</v>
       </c>
       <c r="E139" s="14" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F139" s="15" t="n">
-        <v>29087.68</v>
+        <v>4089343.97</v>
       </c>
     </row>
     <row r="140">
@@ -4417,22 +4417,22 @@
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C140" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D140" s="10" t="n">
-        <v>888</v>
+        <v>29</v>
       </c>
       <c r="E140" s="10" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>12421446.93</v>
+        <v>29087.68</v>
       </c>
     </row>
     <row r="141">
@@ -4448,17 +4448,17 @@
       </c>
       <c r="C141" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
-        <v>201</v>
+        <v>895</v>
       </c>
       <c r="E141" s="14" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="F141" s="15" t="n">
-        <v>2270018.62</v>
+        <v>12550466.81</v>
       </c>
     </row>
     <row r="142">
@@ -4474,43 +4474,43 @@
       </c>
       <c r="C142" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D142" s="10" t="n">
-        <v>59</v>
+        <v>202</v>
       </c>
       <c r="E142" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>775859.87</v>
+        <v>2285954.39</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Assuntos Jurídicos e Patrimônio</t>
+          <t>Secretaria de Administração</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C143" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D143" s="14" t="n">
-        <v>143</v>
+        <v>59</v>
       </c>
       <c r="E143" s="14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F143" s="15" t="n">
-        <v>737278.72</v>
+        <v>775859.87</v>
       </c>
     </row>
     <row r="144">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C144" s="9" t="inlineStr">
@@ -4530,13 +4530,13 @@
         </is>
       </c>
       <c r="D144" s="10" t="n">
-        <v>1444</v>
+        <v>144</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>5117251.15</v>
+        <v>745084.79</v>
       </c>
     </row>
     <row r="145">
@@ -4552,17 +4552,17 @@
       </c>
       <c r="C145" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>88</v>
+        <v>1468</v>
       </c>
       <c r="E145" s="14" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="F145" s="15" t="n">
-        <v>1318890.36</v>
+        <v>5234820.95</v>
       </c>
     </row>
     <row r="146">
@@ -4578,17 +4578,17 @@
       </c>
       <c r="C146" s="9" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D146" s="10" t="n">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="E146" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>17458.96</v>
+        <v>1329882.55</v>
       </c>
     </row>
     <row r="147">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C147" s="13" t="inlineStr">
@@ -4608,13 +4608,13 @@
         </is>
       </c>
       <c r="D147" s="14" t="n">
-        <v>508</v>
+        <v>19</v>
       </c>
       <c r="E147" s="14" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="F147" s="15" t="n">
-        <v>513341.84</v>
+        <v>17458.96</v>
       </c>
     </row>
     <row r="148">
@@ -4630,17 +4630,17 @@
       </c>
       <c r="C148" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D148" s="10" t="n">
-        <v>29</v>
+        <v>527</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>75804.92999999999</v>
+        <v>533106.72</v>
       </c>
     </row>
     <row r="149">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C149" s="13" t="inlineStr">
@@ -4660,13 +4660,13 @@
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>3834</v>
+        <v>29</v>
       </c>
       <c r="E149" s="14" t="n">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="F149" s="15" t="n">
-        <v>65794692.78</v>
+        <v>75804.92999999999</v>
       </c>
     </row>
     <row r="150">
@@ -4682,17 +4682,17 @@
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D150" s="10" t="n">
-        <v>1594</v>
+        <v>3892</v>
       </c>
       <c r="E150" s="10" t="n">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>16606110.22</v>
+        <v>67181562.44</v>
       </c>
     </row>
     <row r="151">
@@ -4708,17 +4708,17 @@
       </c>
       <c r="C151" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D151" s="14" t="n">
-        <v>93</v>
+        <v>1619</v>
       </c>
       <c r="E151" s="14" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F151" s="15" t="n">
-        <v>1342553.22</v>
+        <v>17010148.38</v>
       </c>
     </row>
     <row r="152">
@@ -4734,17 +4734,17 @@
       </c>
       <c r="C152" s="9" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D152" s="10" t="n">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>22276.32</v>
+        <v>1342553.22</v>
       </c>
     </row>
     <row r="153">
@@ -4755,22 +4755,22 @@
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C153" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D153" s="14" t="n">
-        <v>976</v>
+        <v>27</v>
       </c>
       <c r="E153" s="14" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F153" s="15" t="n">
-        <v>30463241.74</v>
+        <v>22276.32</v>
       </c>
     </row>
     <row r="154">
@@ -4786,17 +4786,17 @@
       </c>
       <c r="C154" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D154" s="10" t="n">
-        <v>110</v>
+        <v>992</v>
       </c>
       <c r="E154" s="10" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>2340358.75</v>
+        <v>31055302.25</v>
       </c>
     </row>
     <row r="155">
@@ -4807,33 +4807,33 @@
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C155" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="E155" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F155" s="15" t="n">
-        <v>2628298.71</v>
+        <v>2366530.45</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Comunicação</t>
+          <t>Secretaria de Assuntos Jurídicos e Patrimônio</t>
         </is>
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C156" s="9" t="inlineStr">
@@ -4842,13 +4842,13 @@
         </is>
       </c>
       <c r="D156" s="10" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E156" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>352925.9</v>
+        <v>2684823.31</v>
       </c>
     </row>
     <row r="157">
@@ -4859,22 +4859,22 @@
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C157" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D157" s="14" t="n">
-        <v>290</v>
+        <v>94</v>
       </c>
       <c r="E157" s="14" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F157" s="15" t="n">
-        <v>295078</v>
+        <v>369309.54</v>
       </c>
     </row>
     <row r="158">
@@ -4885,22 +4885,22 @@
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C158" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D158" s="10" t="n">
-        <v>779</v>
+        <v>295</v>
       </c>
       <c r="E158" s="10" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>7725205.8</v>
+        <v>300471.2</v>
       </c>
     </row>
     <row r="159">
@@ -4916,17 +4916,17 @@
       </c>
       <c r="C159" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>485</v>
+        <v>791</v>
       </c>
       <c r="E159" s="14" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F159" s="15" t="n">
-        <v>6903168.67</v>
+        <v>7888616.2</v>
       </c>
     </row>
     <row r="160">
@@ -4942,17 +4942,17 @@
       </c>
       <c r="C160" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D160" s="10" t="n">
-        <v>288</v>
+        <v>497</v>
       </c>
       <c r="E160" s="10" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>2379082.59</v>
+        <v>7063563.19</v>
       </c>
     </row>
     <row r="161">
@@ -4963,22 +4963,22 @@
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C161" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>105</v>
+        <v>291</v>
       </c>
       <c r="E161" s="14" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F161" s="15" t="n">
-        <v>1229751.73</v>
+        <v>2418480.13</v>
       </c>
     </row>
     <row r="162">
@@ -4994,17 +4994,17 @@
       </c>
       <c r="C162" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D162" s="10" t="n">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="E162" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>730305.66</v>
+        <v>1246110.68</v>
       </c>
     </row>
     <row r="163">
@@ -5020,43 +5020,43 @@
       </c>
       <c r="C163" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D163" s="14" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E163" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F163" s="15" t="n">
-        <v>148834.46</v>
+        <v>730305.66</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Cultura</t>
+          <t>Secretaria de Comunicação</t>
         </is>
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C164" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D164" s="10" t="n">
-        <v>121</v>
+        <v>13</v>
       </c>
       <c r="E164" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>467362.96</v>
+        <v>148834.46</v>
       </c>
     </row>
     <row r="165">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C165" s="13" t="inlineStr">
@@ -5076,13 +5076,13 @@
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>184</v>
+        <v>122</v>
       </c>
       <c r="E165" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F165" s="15" t="n">
-        <v>502061.11</v>
+        <v>471139.54</v>
       </c>
     </row>
     <row r="166">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C166" s="9" t="inlineStr">
@@ -5102,13 +5102,13 @@
         </is>
       </c>
       <c r="D166" s="10" t="n">
-        <v>70</v>
+        <v>186</v>
       </c>
       <c r="E166" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>380224.74</v>
+        <v>511438.71</v>
       </c>
     </row>
     <row r="167">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C167" s="13" t="inlineStr">
@@ -5128,13 +5128,13 @@
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>1080</v>
+        <v>71</v>
       </c>
       <c r="E167" s="14" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="F167" s="15" t="n">
-        <v>4692577.29</v>
+        <v>387834.6</v>
       </c>
     </row>
     <row r="168">
@@ -5150,17 +5150,17 @@
       </c>
       <c r="C168" s="9" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D168" s="10" t="n">
-        <v>58</v>
+        <v>1098</v>
       </c>
       <c r="E168" s="10" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>59853.44</v>
+        <v>4788199.6</v>
       </c>
     </row>
     <row r="169">
@@ -5171,22 +5171,22 @@
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C169" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>154</v>
+        <v>59</v>
       </c>
       <c r="E169" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F169" s="15" t="n">
-        <v>1241677.26</v>
+        <v>60938.24</v>
       </c>
     </row>
     <row r="170">
@@ -5202,17 +5202,17 @@
       </c>
       <c r="C170" s="9" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D170" s="10" t="n">
-        <v>962</v>
+        <v>157</v>
       </c>
       <c r="E170" s="10" t="n">
-        <v>101</v>
+        <v>3</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>969101.73</v>
+        <v>1269013.11</v>
       </c>
     </row>
     <row r="171">
@@ -5228,17 +5228,17 @@
       </c>
       <c r="C171" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>51</v>
+        <v>980</v>
       </c>
       <c r="E171" s="14" t="n">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="F171" s="15" t="n">
-        <v>398026.97</v>
+        <v>988628.13</v>
       </c>
     </row>
     <row r="172">
@@ -5249,22 +5249,22 @@
       </c>
       <c r="B172" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C172" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D172" s="10" t="n">
-        <v>746</v>
+        <v>51</v>
       </c>
       <c r="E172" s="10" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>4923072.14</v>
+        <v>398026.97</v>
       </c>
     </row>
     <row r="173">
@@ -5280,17 +5280,17 @@
       </c>
       <c r="C173" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>290</v>
+        <v>761</v>
       </c>
       <c r="E173" s="14" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F173" s="15" t="n">
-        <v>4288825.52</v>
+        <v>5063946.98</v>
       </c>
     </row>
     <row r="174">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="C174" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D174" s="10" t="n">
-        <v>345</v>
+        <v>297</v>
       </c>
       <c r="E174" s="10" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>3818952.33</v>
+        <v>4383795.05</v>
       </c>
     </row>
     <row r="175">
@@ -5332,17 +5332,17 @@
       </c>
       <c r="C175" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>43</v>
+        <v>351</v>
       </c>
       <c r="E175" s="14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F175" s="15" t="n">
-        <v>43923.2</v>
+        <v>3906137.53</v>
       </c>
     </row>
     <row r="176">
@@ -5353,22 +5353,22 @@
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C176" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D176" s="10" t="n">
-        <v>332</v>
+        <v>43</v>
       </c>
       <c r="E176" s="10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>3780948.83</v>
+        <v>43923.2</v>
       </c>
     </row>
     <row r="177">
@@ -5384,17 +5384,17 @@
       </c>
       <c r="C177" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
-        <v>78</v>
+        <v>335</v>
       </c>
       <c r="E177" s="14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F177" s="15" t="n">
-        <v>1029711.3</v>
+        <v>3821998.6</v>
       </c>
     </row>
     <row r="178">
@@ -5405,22 +5405,22 @@
       </c>
       <c r="B178" s="8" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C178" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D178" s="10" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E178" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>892568.84</v>
+        <v>1047160.76</v>
       </c>
     </row>
     <row r="179">
@@ -5436,43 +5436,43 @@
       </c>
       <c r="C179" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D179" s="14" t="n">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="E179" s="14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F179" s="15" t="n">
-        <v>370947.32</v>
+        <v>919812.12</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Desenvolvimento Econômico, Trabalho e Turismo</t>
+          <t>Secretaria de Cultura</t>
         </is>
       </c>
       <c r="B180" s="8" t="inlineStr">
         <is>
-          <t>Sem escolaridade formal registrada</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C180" s="9" t="inlineStr">
         <is>
-          <t>inativos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D180" s="10" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="E180" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>48748.72</v>
+        <v>386083.01</v>
       </c>
     </row>
     <row r="181">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Sem escolaridade formal registrada</t>
         </is>
       </c>
       <c r="C181" s="13" t="inlineStr">
@@ -5492,13 +5492,13 @@
         </is>
       </c>
       <c r="D181" s="14" t="n">
-        <v>280</v>
+        <v>14</v>
       </c>
       <c r="E181" s="14" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F181" s="15" t="n">
-        <v>972072.78</v>
+        <v>48748.72</v>
       </c>
     </row>
     <row r="182">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="B182" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C182" s="9" t="inlineStr">
@@ -5518,13 +5518,13 @@
         </is>
       </c>
       <c r="D182" s="10" t="n">
-        <v>673</v>
+        <v>280</v>
       </c>
       <c r="E182" s="10" t="n">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>3456661.38</v>
+        <v>972072.78</v>
       </c>
     </row>
     <row r="183">
@@ -5540,17 +5540,17 @@
       </c>
       <c r="C183" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>inativos</t>
         </is>
       </c>
       <c r="D183" s="14" t="n">
-        <v>32</v>
+        <v>673</v>
       </c>
       <c r="E183" s="14" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="F183" s="15" t="n">
-        <v>67574.05</v>
+        <v>3456661.38</v>
       </c>
     </row>
     <row r="184">
@@ -5561,22 +5561,22 @@
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C184" s="9" t="inlineStr">
         <is>
-          <t>inativos</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D184" s="10" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="E184" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>37967.67</v>
+        <v>67574.05</v>
       </c>
     </row>
     <row r="185">
@@ -5592,17 +5592,17 @@
       </c>
       <c r="C185" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>inativos</t>
         </is>
       </c>
       <c r="D185" s="14" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E185" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F185" s="15" t="n">
-        <v>21780.4</v>
+        <v>37967.67</v>
       </c>
     </row>
     <row r="186">
@@ -5613,22 +5613,22 @@
       </c>
       <c r="B186" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C186" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D186" s="10" t="n">
-        <v>354</v>
+        <v>20</v>
       </c>
       <c r="E186" s="10" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>1454749.46</v>
+        <v>21780.4</v>
       </c>
     </row>
     <row r="187">
@@ -5644,17 +5644,17 @@
       </c>
       <c r="C187" s="13" t="inlineStr">
         <is>
-          <t>inativos</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D187" s="14" t="n">
-        <v>155</v>
+        <v>354</v>
       </c>
       <c r="E187" s="14" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F187" s="15" t="n">
-        <v>1123145.04</v>
+        <v>1454749.46</v>
       </c>
     </row>
     <row r="188">
@@ -5670,17 +5670,17 @@
       </c>
       <c r="C188" s="9" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>inativos</t>
         </is>
       </c>
       <c r="D188" s="10" t="n">
-        <v>45</v>
+        <v>155</v>
       </c>
       <c r="E188" s="10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>43719.36</v>
+        <v>1123145.04</v>
       </c>
     </row>
     <row r="189">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C189" s="13" t="inlineStr">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="D189" s="14" t="n">
-        <v>333</v>
+        <v>45</v>
       </c>
       <c r="E189" s="14" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="F189" s="15" t="n">
-        <v>331067.84</v>
+        <v>43719.36</v>
       </c>
     </row>
     <row r="190">
@@ -5722,17 +5722,17 @@
       </c>
       <c r="C190" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D190" s="10" t="n">
-        <v>6</v>
+        <v>338</v>
       </c>
       <c r="E190" s="10" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="F190" s="11" t="n">
-        <v>96751.09</v>
+        <v>336311.84</v>
       </c>
     </row>
     <row r="191">
@@ -5748,17 +5748,17 @@
       </c>
       <c r="C191" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D191" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E191" s="14" t="n">
         <v>1</v>
       </c>
       <c r="F191" s="15" t="n">
-        <v>71649.52</v>
+        <v>96751.09</v>
       </c>
     </row>
     <row r="192">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="B192" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C192" s="9" t="inlineStr">
@@ -5778,13 +5778,13 @@
         </is>
       </c>
       <c r="D192" s="10" t="n">
-        <v>1110</v>
+        <v>13</v>
       </c>
       <c r="E192" s="10" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="F192" s="11" t="n">
-        <v>7655735.25</v>
+        <v>71649.52</v>
       </c>
     </row>
     <row r="193">
@@ -5800,17 +5800,17 @@
       </c>
       <c r="C193" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D193" s="14" t="n">
-        <v>625</v>
+        <v>1117</v>
       </c>
       <c r="E193" s="14" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="F193" s="15" t="n">
-        <v>6003043.14</v>
+        <v>7749895.92</v>
       </c>
     </row>
     <row r="194">
@@ -5826,17 +5826,17 @@
       </c>
       <c r="C194" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D194" s="10" t="n">
-        <v>167</v>
+        <v>629</v>
       </c>
       <c r="E194" s="10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F194" s="11" t="n">
-        <v>2567575.85</v>
+        <v>6054450.18</v>
       </c>
     </row>
     <row r="195">
@@ -5852,17 +5852,17 @@
       </c>
       <c r="C195" s="13" t="inlineStr">
         <is>
-          <t>inativos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D195" s="14" t="n">
-        <v>102</v>
+        <v>171</v>
       </c>
       <c r="E195" s="14" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F195" s="15" t="n">
-        <v>1220503.93</v>
+        <v>2638452.2</v>
       </c>
     </row>
     <row r="196">
@@ -5873,22 +5873,22 @@
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C196" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>inativos</t>
         </is>
       </c>
       <c r="D196" s="10" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="E196" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F196" s="11" t="n">
-        <v>1630907.1</v>
+        <v>1220503.93</v>
       </c>
     </row>
     <row r="197">
@@ -5904,17 +5904,17 @@
       </c>
       <c r="C197" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D197" s="14" t="n">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="E197" s="14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F197" s="15" t="n">
-        <v>1592368.32</v>
+        <v>1630907.1</v>
       </c>
     </row>
     <row r="198">
@@ -5930,43 +5930,43 @@
       </c>
       <c r="C198" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D198" s="10" t="n">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="E198" s="10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F198" s="11" t="n">
-        <v>457749.49</v>
+        <v>1592368.32</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Empreendedorismo da Micro e Pequena Empresa</t>
+          <t>Secretaria de Desenvolvimento Econômico, Trabalho e Turismo</t>
         </is>
       </c>
       <c r="B199" s="12" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C199" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D199" s="14" t="n">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="E199" s="14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F199" s="15" t="n">
-        <v>271480.11</v>
+        <v>457749.49</v>
       </c>
     </row>
     <row r="200">
@@ -5977,22 +5977,22 @@
       </c>
       <c r="B200" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C200" s="9" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D200" s="10" t="n">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="E200" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F200" s="11" t="n">
-        <v>13379.2</v>
+        <v>297862.62</v>
       </c>
     </row>
     <row r="201">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="B201" s="12" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C201" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D201" s="14" t="n">
-        <v>158</v>
+        <v>16</v>
       </c>
       <c r="E201" s="14" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F201" s="15" t="n">
-        <v>1662136.95</v>
+        <v>16633.6</v>
       </c>
     </row>
     <row r="202">
@@ -6034,17 +6034,17 @@
       </c>
       <c r="C202" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D202" s="10" t="n">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="E202" s="10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F202" s="11" t="n">
-        <v>1476487.71</v>
+        <v>1767184.06</v>
       </c>
     </row>
     <row r="203">
@@ -6060,17 +6060,17 @@
       </c>
       <c r="C203" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D203" s="14" t="n">
-        <v>49</v>
+        <v>198</v>
       </c>
       <c r="E203" s="14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F203" s="15" t="n">
-        <v>754495.74</v>
+        <v>1552829.39</v>
       </c>
     </row>
     <row r="204">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="B204" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C204" s="9" t="inlineStr">
@@ -6090,39 +6090,39 @@
         </is>
       </c>
       <c r="D204" s="10" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="E204" s="10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F204" s="11" t="n">
-        <v>700864.0600000001</v>
+        <v>858461.54</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Esportes e Lazer</t>
+          <t>Secretaria de Empreendedorismo da Micro e Pequena Empresa</t>
         </is>
       </c>
       <c r="B205" s="12" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C205" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D205" s="14" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="E205" s="14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F205" s="15" t="n">
-        <v>506760.3</v>
+        <v>700864.0600000001</v>
       </c>
     </row>
     <row r="206">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="B206" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C206" s="9" t="inlineStr">
@@ -6142,13 +6142,13 @@
         </is>
       </c>
       <c r="D206" s="10" t="n">
-        <v>381</v>
+        <v>95</v>
       </c>
       <c r="E206" s="10" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F206" s="11" t="n">
-        <v>1697825.17</v>
+        <v>506760.3</v>
       </c>
     </row>
     <row r="207">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="B207" s="12" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C207" s="13" t="inlineStr">
@@ -6168,13 +6168,13 @@
         </is>
       </c>
       <c r="D207" s="14" t="n">
-        <v>714</v>
+        <v>390</v>
       </c>
       <c r="E207" s="14" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F207" s="15" t="n">
-        <v>3995733.14</v>
+        <v>1742020.59</v>
       </c>
     </row>
     <row r="208">
@@ -6190,17 +6190,17 @@
       </c>
       <c r="C208" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D208" s="10" t="n">
-        <v>15</v>
+        <v>731</v>
       </c>
       <c r="E208" s="10" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="F208" s="11" t="n">
-        <v>132025.25</v>
+        <v>4095926.97</v>
       </c>
     </row>
     <row r="209">
@@ -6216,17 +6216,17 @@
       </c>
       <c r="C209" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D209" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="E209" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E209" s="14" t="n">
-        <v>1</v>
-      </c>
       <c r="F209" s="15" t="n">
-        <v>21043.48</v>
+        <v>148620.08</v>
       </c>
     </row>
     <row r="210">
@@ -6237,22 +6237,22 @@
       </c>
       <c r="B210" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C210" s="9" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D210" s="10" t="n">
-        <v>645</v>
+        <v>2</v>
       </c>
       <c r="E210" s="10" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="F210" s="11" t="n">
-        <v>677249.72</v>
+        <v>21043.48</v>
       </c>
     </row>
     <row r="211">
@@ -6268,17 +6268,17 @@
       </c>
       <c r="C211" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D211" s="14" t="n">
-        <v>13</v>
+        <v>655</v>
       </c>
       <c r="E211" s="14" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="F211" s="15" t="n">
-        <v>219007.63</v>
+        <v>688123.48</v>
       </c>
     </row>
     <row r="212">
@@ -6294,17 +6294,17 @@
       </c>
       <c r="C212" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D212" s="10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E212" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F212" s="11" t="n">
-        <v>113924.19</v>
+        <v>219007.63</v>
       </c>
     </row>
     <row r="213">
@@ -6320,17 +6320,17 @@
       </c>
       <c r="C213" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D213" s="14" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E213" s="14" t="n">
         <v>1</v>
       </c>
       <c r="F213" s="15" t="n">
-        <v>8822.08</v>
+        <v>113924.19</v>
       </c>
     </row>
     <row r="214">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="B214" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C214" s="9" t="inlineStr">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="D214" s="10" t="n">
-        <v>2031</v>
+        <v>1</v>
       </c>
       <c r="E214" s="10" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F214" s="11" t="n">
-        <v>20994943.41</v>
+        <v>8822.08</v>
       </c>
     </row>
     <row r="215">
@@ -6372,17 +6372,17 @@
       </c>
       <c r="C215" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D215" s="14" t="n">
-        <v>375</v>
+        <v>2067</v>
       </c>
       <c r="E215" s="14" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F215" s="15" t="n">
-        <v>5387365.58</v>
+        <v>21428399.59</v>
       </c>
     </row>
     <row r="216">
@@ -6398,17 +6398,17 @@
       </c>
       <c r="C216" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D216" s="10" t="n">
-        <v>539</v>
+        <v>387</v>
       </c>
       <c r="E216" s="10" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F216" s="11" t="n">
-        <v>4451761.05</v>
+        <v>5543914.14</v>
       </c>
     </row>
     <row r="217">
@@ -6424,17 +6424,17 @@
       </c>
       <c r="C217" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D217" s="14" t="n">
-        <v>14</v>
+        <v>546</v>
       </c>
       <c r="E217" s="14" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F217" s="15" t="n">
-        <v>14108.32</v>
+        <v>4529761.19</v>
       </c>
     </row>
     <row r="218">
@@ -6445,22 +6445,22 @@
       </c>
       <c r="B218" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C218" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D218" s="10" t="n">
-        <v>812</v>
+        <v>14</v>
       </c>
       <c r="E218" s="10" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F218" s="11" t="n">
-        <v>9304930.5</v>
+        <v>14108.32</v>
       </c>
     </row>
     <row r="219">
@@ -6476,17 +6476,17 @@
       </c>
       <c r="C219" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D219" s="14" t="n">
-        <v>75</v>
+        <v>822</v>
       </c>
       <c r="E219" s="14" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F219" s="15" t="n">
-        <v>858499.47</v>
+        <v>9597331.470000001</v>
       </c>
     </row>
     <row r="220">
@@ -6502,17 +6502,17 @@
       </c>
       <c r="C220" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D220" s="10" t="n">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="E220" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F220" s="11" t="n">
-        <v>45669.68</v>
+        <v>875166.52</v>
       </c>
     </row>
     <row r="221">
@@ -6523,22 +6523,22 @@
       </c>
       <c r="B221" s="12" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C221" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D221" s="14" t="n">
-        <v>137</v>
+        <v>4</v>
       </c>
       <c r="E221" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F221" s="15" t="n">
-        <v>1683119.71</v>
+        <v>45669.68</v>
       </c>
     </row>
     <row r="222">
@@ -6554,28 +6554,28 @@
       </c>
       <c r="C222" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D222" s="10" t="n">
-        <v>4</v>
+        <v>138</v>
       </c>
       <c r="E222" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F222" s="11" t="n">
-        <v>70024.88</v>
+        <v>1699857.28</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Gabinete Central</t>
+          <t>Secretaria de Esportes e Lazer</t>
         </is>
       </c>
       <c r="B223" s="12" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C223" s="13" t="inlineStr">
@@ -6584,13 +6584,13 @@
         </is>
       </c>
       <c r="D223" s="14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E223" s="14" t="n">
         <v>1</v>
       </c>
       <c r="F223" s="15" t="n">
-        <v>454.86</v>
+        <v>70024.88</v>
       </c>
     </row>
     <row r="224">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="B224" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C224" s="9" t="inlineStr">
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="D224" s="10" t="n">
-        <v>732</v>
+        <v>1</v>
       </c>
       <c r="E224" s="10" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="F224" s="11" t="n">
-        <v>3097653.14</v>
+        <v>454.86</v>
       </c>
     </row>
     <row r="225">
@@ -6632,17 +6632,17 @@
       </c>
       <c r="C225" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D225" s="14" t="n">
-        <v>44</v>
+        <v>759</v>
       </c>
       <c r="E225" s="14" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="F225" s="15" t="n">
-        <v>415407.35</v>
+        <v>3217500.61</v>
       </c>
     </row>
     <row r="226">
@@ -6658,17 +6658,17 @@
       </c>
       <c r="C226" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D226" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="E226" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E226" s="10" t="n">
-        <v>1</v>
-      </c>
       <c r="F226" s="11" t="n">
-        <v>32832.28</v>
+        <v>441399.27</v>
       </c>
     </row>
     <row r="227">
@@ -6688,13 +6688,13 @@
         </is>
       </c>
       <c r="D227" s="14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E227" s="14" t="n">
         <v>3</v>
       </c>
       <c r="F227" s="15" t="n">
-        <v>32266.8</v>
+        <v>33351.6</v>
       </c>
     </row>
     <row r="228">
@@ -6705,22 +6705,22 @@
       </c>
       <c r="B228" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C228" s="9" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D228" s="10" t="n">
-        <v>476</v>
+        <v>3</v>
       </c>
       <c r="E228" s="10" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="F228" s="11" t="n">
-        <v>476710.96</v>
+        <v>32832.28</v>
       </c>
     </row>
     <row r="229">
@@ -6736,17 +6736,17 @@
       </c>
       <c r="C229" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D229" s="14" t="n">
-        <v>6</v>
+        <v>512</v>
       </c>
       <c r="E229" s="14" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="F229" s="15" t="n">
-        <v>34717.68</v>
+        <v>513679.36</v>
       </c>
     </row>
     <row r="230">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="B230" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C230" s="9" t="inlineStr">
@@ -6766,13 +6766,13 @@
         </is>
       </c>
       <c r="D230" s="10" t="n">
-        <v>2475</v>
+        <v>7</v>
       </c>
       <c r="E230" s="10" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="F230" s="11" t="n">
-        <v>23118191.64</v>
+        <v>39566.32</v>
       </c>
     </row>
     <row r="231">
@@ -6788,17 +6788,17 @@
       </c>
       <c r="C231" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D231" s="14" t="n">
-        <v>1441</v>
+        <v>2537</v>
       </c>
       <c r="E231" s="14" t="n">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="F231" s="15" t="n">
-        <v>17055549.62</v>
+        <v>23846203.51</v>
       </c>
     </row>
     <row r="232">
@@ -6814,17 +6814,17 @@
       </c>
       <c r="C232" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D232" s="10" t="n">
-        <v>467</v>
+        <v>1465</v>
       </c>
       <c r="E232" s="10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F232" s="11" t="n">
-        <v>6863390.24</v>
+        <v>17490266.21</v>
       </c>
     </row>
     <row r="233">
@@ -6835,22 +6835,22 @@
       </c>
       <c r="B233" s="12" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C233" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D233" s="14" t="n">
-        <v>640</v>
+        <v>476</v>
       </c>
       <c r="E233" s="14" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="F233" s="15" t="n">
-        <v>9049588.67</v>
+        <v>7018783.2</v>
       </c>
     </row>
     <row r="234">
@@ -6866,17 +6866,17 @@
       </c>
       <c r="C234" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D234" s="10" t="n">
-        <v>202</v>
+        <v>652</v>
       </c>
       <c r="E234" s="10" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F234" s="11" t="n">
-        <v>2635709.58</v>
+        <v>9269227.029999999</v>
       </c>
     </row>
     <row r="235">
@@ -6892,17 +6892,17 @@
       </c>
       <c r="C235" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D235" s="14" t="n">
-        <v>119</v>
+        <v>204</v>
       </c>
       <c r="E235" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F235" s="15" t="n">
-        <v>2062898.41</v>
+        <v>2664311.62</v>
       </c>
     </row>
     <row r="236">
@@ -6913,33 +6913,33 @@
       </c>
       <c r="B236" s="8" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C236" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D236" s="10" t="n">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="E236" s="10" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F236" s="11" t="n">
-        <v>1397905.78</v>
+        <v>2095053.61</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Governo</t>
+          <t>Secretaria de Gabinete Central</t>
         </is>
       </c>
       <c r="B237" s="12" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C237" s="13" t="inlineStr">
@@ -6948,13 +6948,13 @@
         </is>
       </c>
       <c r="D237" s="14" t="n">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="E237" s="14" t="n">
         <v>1</v>
       </c>
       <c r="F237" s="15" t="n">
-        <v>183474.85</v>
+        <v>1423593.4</v>
       </c>
     </row>
     <row r="238">
@@ -6965,22 +6965,22 @@
       </c>
       <c r="B238" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C238" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D238" s="10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E238" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F238" s="11" t="n">
-        <v>144873.19</v>
+        <v>183474.85</v>
       </c>
     </row>
     <row r="239">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="B239" s="12" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C239" s="13" t="inlineStr">
@@ -7000,13 +7000,13 @@
         </is>
       </c>
       <c r="D239" s="14" t="n">
-        <v>663</v>
+        <v>24</v>
       </c>
       <c r="E239" s="14" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="F239" s="15" t="n">
-        <v>4493459.6</v>
+        <v>144873.19</v>
       </c>
     </row>
     <row r="240">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="C240" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D240" s="10" t="n">
-        <v>33</v>
+        <v>684</v>
       </c>
       <c r="E240" s="10" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="F240" s="11" t="n">
-        <v>569656.15</v>
+        <v>4627902.21</v>
       </c>
     </row>
     <row r="241">
@@ -7048,17 +7048,17 @@
       </c>
       <c r="C241" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D241" s="14" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E241" s="14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F241" s="15" t="n">
-        <v>219514.74</v>
+        <v>569656.15</v>
       </c>
     </row>
     <row r="242">
@@ -7074,17 +7074,17 @@
       </c>
       <c r="C242" s="9" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D242" s="10" t="n">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="E242" s="10" t="n">
         <v>6</v>
       </c>
       <c r="F242" s="11" t="n">
-        <v>75136.88</v>
+        <v>283156.8</v>
       </c>
     </row>
     <row r="243">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="B243" s="12" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C243" s="13" t="inlineStr">
@@ -7104,13 +7104,13 @@
         </is>
       </c>
       <c r="D243" s="14" t="n">
-        <v>1390</v>
+        <v>71</v>
       </c>
       <c r="E243" s="14" t="n">
-        <v>174</v>
+        <v>6</v>
       </c>
       <c r="F243" s="15" t="n">
-        <v>1399557.28</v>
+        <v>75136.88</v>
       </c>
     </row>
     <row r="244">
@@ -7126,17 +7126,17 @@
       </c>
       <c r="C244" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D244" s="10" t="n">
-        <v>62</v>
+        <v>1409</v>
       </c>
       <c r="E244" s="10" t="n">
-        <v>2</v>
+        <v>176</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>310420.11</v>
+        <v>1417989.52</v>
       </c>
     </row>
     <row r="245">
@@ -7152,17 +7152,17 @@
       </c>
       <c r="C245" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D245" s="14" t="n">
+        <v>63</v>
+      </c>
+      <c r="E245" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E245" s="14" t="n">
-        <v>1</v>
-      </c>
       <c r="F245" s="15" t="n">
-        <v>20422.13</v>
+        <v>317687.58</v>
       </c>
     </row>
     <row r="246">
@@ -7173,22 +7173,22 @@
       </c>
       <c r="B246" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C246" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D246" s="10" t="n">
-        <v>1888</v>
+        <v>2</v>
       </c>
       <c r="E246" s="10" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>23498869.83</v>
+        <v>20422.13</v>
       </c>
     </row>
     <row r="247">
@@ -7204,17 +7204,17 @@
       </c>
       <c r="C247" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D247" s="14" t="n">
-        <v>1296</v>
+        <v>1919</v>
       </c>
       <c r="E247" s="14" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="F247" s="15" t="n">
-        <v>18350576.68</v>
+        <v>24004119.91</v>
       </c>
     </row>
     <row r="248">
@@ -7230,17 +7230,17 @@
       </c>
       <c r="C248" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D248" s="10" t="n">
-        <v>1582</v>
+        <v>1318</v>
       </c>
       <c r="E248" s="10" t="n">
-        <v>75</v>
+        <v>146</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>17179199.73</v>
+        <v>18713346.36</v>
       </c>
     </row>
     <row r="249">
@@ -7256,17 +7256,17 @@
       </c>
       <c r="C249" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D249" s="14" t="n">
-        <v>3</v>
+        <v>1606</v>
       </c>
       <c r="E249" s="14" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="F249" s="15" t="n">
-        <v>600</v>
+        <v>17505143.65</v>
       </c>
     </row>
     <row r="250">
@@ -7277,22 +7277,22 @@
       </c>
       <c r="B250" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C250" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D250" s="10" t="n">
-        <v>214</v>
+        <v>3</v>
       </c>
       <c r="E250" s="10" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>6061706.05</v>
+        <v>600</v>
       </c>
     </row>
     <row r="251">
@@ -7308,17 +7308,17 @@
       </c>
       <c r="C251" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D251" s="14" t="n">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="E251" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F251" s="15" t="n">
-        <v>2801650.88</v>
+        <v>6203132.39</v>
       </c>
     </row>
     <row r="252">
@@ -7334,17 +7334,17 @@
       </c>
       <c r="C252" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D252" s="10" t="n">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="E252" s="10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F252" s="11" t="n">
-        <v>1440248.13</v>
+        <v>2923179.31</v>
       </c>
     </row>
     <row r="253">
@@ -7360,17 +7360,17 @@
       </c>
       <c r="C253" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D253" s="14" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="E253" s="14" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F253" s="15" t="n">
-        <v>72.31999999999999</v>
+        <v>1455700.92</v>
       </c>
     </row>
     <row r="254">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="B254" s="8" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C254" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D254" s="10" t="n">
@@ -7396,33 +7396,33 @@
         <v>1</v>
       </c>
       <c r="F254" s="11" t="n">
-        <v>30501.14</v>
+        <v>72.31999999999999</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Inclusão e Transtorno do Espectro Autista</t>
+          <t>Secretaria de Governo</t>
         </is>
       </c>
       <c r="B255" s="12" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C255" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D255" s="14" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E255" s="14" t="n">
         <v>1</v>
       </c>
       <c r="F255" s="15" t="n">
-        <v>185120.07</v>
+        <v>30501.14</v>
       </c>
     </row>
     <row r="256">
@@ -7438,17 +7438,17 @@
       </c>
       <c r="C256" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D256" s="10" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E256" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F256" s="11" t="n">
-        <v>160325.35</v>
+        <v>185120.07</v>
       </c>
     </row>
     <row r="257">
@@ -7459,22 +7459,22 @@
       </c>
       <c r="B257" s="12" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C257" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D257" s="14" t="n">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="E257" s="14" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F257" s="15" t="n">
-        <v>1357146.96</v>
+        <v>173289.62</v>
       </c>
     </row>
     <row r="258">
@@ -7490,17 +7490,17 @@
       </c>
       <c r="C258" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D258" s="10" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E258" s="10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F258" s="11" t="n">
-        <v>1124757.3</v>
+        <v>1445715.17</v>
       </c>
     </row>
     <row r="259">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="C259" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D259" s="14" t="n">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="E259" s="14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F259" s="15" t="n">
-        <v>20533.61</v>
+        <v>1175217.7</v>
       </c>
     </row>
     <row r="260">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B260" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C260" s="9" t="inlineStr">
@@ -7546,24 +7546,24 @@
         </is>
       </c>
       <c r="D260" s="10" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E260" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F260" s="11" t="n">
-        <v>208782.57</v>
+        <v>20533.61</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Mobilidade</t>
+          <t>Secretaria de Inclusão e Transtorno do Espectro Autista</t>
         </is>
       </c>
       <c r="B261" s="12" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C261" s="13" t="inlineStr">
@@ -7572,13 +7572,13 @@
         </is>
       </c>
       <c r="D261" s="14" t="n">
-        <v>154</v>
+        <v>25</v>
       </c>
       <c r="E261" s="14" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F261" s="15" t="n">
-        <v>876680.49</v>
+        <v>222734.58</v>
       </c>
     </row>
     <row r="262">
@@ -7589,22 +7589,22 @@
       </c>
       <c r="B262" s="8" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C262" s="9" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D262" s="10" t="n">
-        <v>23</v>
+        <v>166</v>
       </c>
       <c r="E262" s="10" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F262" s="11" t="n">
-        <v>22796.4</v>
+        <v>947203.58</v>
       </c>
     </row>
     <row r="263">
@@ -7615,22 +7615,22 @@
       </c>
       <c r="B263" s="12" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C263" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D263" s="14" t="n">
-        <v>431</v>
+        <v>23</v>
       </c>
       <c r="E263" s="14" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="F263" s="15" t="n">
-        <v>3656890.51</v>
+        <v>22796.4</v>
       </c>
     </row>
     <row r="264">
@@ -7646,17 +7646,17 @@
       </c>
       <c r="C264" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D264" s="10" t="n">
-        <v>19</v>
+        <v>457</v>
       </c>
       <c r="E264" s="10" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="F264" s="11" t="n">
-        <v>172072.44</v>
+        <v>3830044</v>
       </c>
     </row>
     <row r="265">
@@ -7672,17 +7672,17 @@
       </c>
       <c r="C265" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D265" s="14" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="E265" s="14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F265" s="15" t="n">
-        <v>42380.88</v>
+        <v>182482.51</v>
       </c>
     </row>
     <row r="266">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="B266" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C266" s="9" t="inlineStr">
@@ -7702,13 +7702,13 @@
         </is>
       </c>
       <c r="D266" s="10" t="n">
-        <v>511</v>
+        <v>48</v>
       </c>
       <c r="E266" s="10" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F266" s="11" t="n">
-        <v>516056.86</v>
+        <v>43130.88</v>
       </c>
     </row>
     <row r="267">
@@ -7724,17 +7724,17 @@
       </c>
       <c r="C267" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D267" s="14" t="n">
-        <v>55</v>
+        <v>522</v>
       </c>
       <c r="E267" s="14" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="F267" s="15" t="n">
-        <v>405136.31</v>
+        <v>526189.1799999999</v>
       </c>
     </row>
     <row r="268">
@@ -7745,22 +7745,22 @@
       </c>
       <c r="B268" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C268" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D268" s="10" t="n">
-        <v>432</v>
+        <v>58</v>
       </c>
       <c r="E268" s="10" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F268" s="11" t="n">
-        <v>6126996.13</v>
+        <v>428997.77</v>
       </c>
     </row>
     <row r="269">
@@ -7776,17 +7776,17 @@
       </c>
       <c r="C269" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D269" s="14" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E269" s="14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F269" s="15" t="n">
-        <v>4604186.1</v>
+        <v>6237945.16</v>
       </c>
     </row>
     <row r="270">
@@ -7802,17 +7802,17 @@
       </c>
       <c r="C270" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D270" s="10" t="n">
-        <v>143</v>
+        <v>445</v>
       </c>
       <c r="E270" s="10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F270" s="11" t="n">
-        <v>1991316.88</v>
+        <v>4693443.01</v>
       </c>
     </row>
     <row r="271">
@@ -7823,22 +7823,22 @@
       </c>
       <c r="B271" s="12" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C271" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D271" s="14" t="n">
-        <v>50</v>
+        <v>147</v>
       </c>
       <c r="E271" s="14" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F271" s="15" t="n">
-        <v>644274.8100000001</v>
+        <v>2061421.95</v>
       </c>
     </row>
     <row r="272">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="B272" s="8" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C272" s="9" t="inlineStr">
@@ -7858,39 +7858,39 @@
         </is>
       </c>
       <c r="D272" s="10" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="E272" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F272" s="11" t="n">
-        <v>375117.73</v>
+        <v>661014.0600000001</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Parcerias</t>
+          <t>Secretaria de Mobilidade</t>
         </is>
       </c>
       <c r="B273" s="12" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C273" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D273" s="14" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E273" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F273" s="15" t="n">
-        <v>330310.78</v>
+        <v>396688.72</v>
       </c>
     </row>
     <row r="274">
@@ -7906,17 +7906,17 @@
       </c>
       <c r="C274" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D274" s="10" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E274" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F274" s="11" t="n">
-        <v>271707.14</v>
+        <v>351130.92</v>
       </c>
     </row>
     <row r="275">
@@ -7927,22 +7927,22 @@
       </c>
       <c r="B275" s="12" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C275" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D275" s="14" t="n">
-        <v>176</v>
+        <v>46</v>
       </c>
       <c r="E275" s="14" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F275" s="15" t="n">
-        <v>182211.44</v>
+        <v>285586.99</v>
       </c>
     </row>
     <row r="276">
@@ -7953,22 +7953,22 @@
       </c>
       <c r="B276" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C276" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D276" s="10" t="n">
-        <v>529</v>
+        <v>187</v>
       </c>
       <c r="E276" s="10" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F276" s="11" t="n">
-        <v>4705066.7</v>
+        <v>193326.24</v>
       </c>
     </row>
     <row r="277">
@@ -7984,17 +7984,17 @@
       </c>
       <c r="C277" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D277" s="14" t="n">
-        <v>139</v>
+        <v>554</v>
       </c>
       <c r="E277" s="14" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F277" s="15" t="n">
-        <v>2333972.91</v>
+        <v>5000860.36</v>
       </c>
     </row>
     <row r="278">
@@ -8010,17 +8010,17 @@
       </c>
       <c r="C278" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D278" s="10" t="n">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="E278" s="10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F278" s="11" t="n">
-        <v>2020966.05</v>
+        <v>2485116.72</v>
       </c>
     </row>
     <row r="279">
@@ -8031,22 +8031,22 @@
       </c>
       <c r="B279" s="12" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C279" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D279" s="14" t="n">
-        <v>76</v>
+        <v>188</v>
       </c>
       <c r="E279" s="14" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F279" s="15" t="n">
-        <v>1044622.29</v>
+        <v>2162868.16</v>
       </c>
     </row>
     <row r="280">
@@ -8062,17 +8062,17 @@
       </c>
       <c r="C280" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D280" s="10" t="n">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="E280" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F280" s="11" t="n">
-        <v>103076.38</v>
+        <v>1110372.35</v>
       </c>
     </row>
     <row r="281">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="C281" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D281" s="14" t="n">
@@ -8098,33 +8098,33 @@
         <v>1</v>
       </c>
       <c r="F281" s="15" t="n">
-        <v>86130.12</v>
+        <v>103076.38</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Planejamento e Desenvolvimento Urbano</t>
+          <t>Secretaria de Parcerias</t>
         </is>
       </c>
       <c r="B282" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C282" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D282" s="10" t="n">
-        <v>128</v>
+        <v>8</v>
       </c>
       <c r="E282" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F282" s="11" t="n">
-        <v>571598.46</v>
+        <v>86130.12</v>
       </c>
     </row>
     <row r="283">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="B283" s="12" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C283" s="13" t="inlineStr">
@@ -8144,13 +8144,13 @@
         </is>
       </c>
       <c r="D283" s="14" t="n">
-        <v>2589</v>
+        <v>130</v>
       </c>
       <c r="E283" s="14" t="n">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="F283" s="15" t="n">
-        <v>16402915.84</v>
+        <v>582277.22</v>
       </c>
     </row>
     <row r="284">
@@ -8166,17 +8166,17 @@
       </c>
       <c r="C284" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D284" s="10" t="n">
-        <v>7</v>
+        <v>2653</v>
       </c>
       <c r="E284" s="10" t="n">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="F284" s="11" t="n">
-        <v>76580.11</v>
+        <v>16875933.82</v>
       </c>
     </row>
     <row r="285">
@@ -8192,17 +8192,17 @@
       </c>
       <c r="C285" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D285" s="14" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E285" s="14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F285" s="15" t="n">
-        <v>19219.52</v>
+        <v>87911</v>
       </c>
     </row>
     <row r="286">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="B286" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C286" s="9" t="inlineStr">
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="D286" s="10" t="n">
-        <v>1433</v>
+        <v>19</v>
       </c>
       <c r="E286" s="10" t="n">
-        <v>129</v>
+        <v>5</v>
       </c>
       <c r="F286" s="11" t="n">
-        <v>1501829.44</v>
+        <v>19219.52</v>
       </c>
     </row>
     <row r="287">
@@ -8244,17 +8244,17 @@
       </c>
       <c r="C287" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D287" s="14" t="n">
-        <v>114</v>
+        <v>1457</v>
       </c>
       <c r="E287" s="14" t="n">
-        <v>2</v>
+        <v>131</v>
       </c>
       <c r="F287" s="15" t="n">
-        <v>607489.4</v>
+        <v>1526674.88</v>
       </c>
     </row>
     <row r="288">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="B288" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C288" s="9" t="inlineStr">
@@ -8274,13 +8274,13 @@
         </is>
       </c>
       <c r="D288" s="10" t="n">
-        <v>3852</v>
+        <v>117</v>
       </c>
       <c r="E288" s="10" t="n">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="F288" s="11" t="n">
-        <v>32611338.54</v>
+        <v>621870.29</v>
       </c>
     </row>
     <row r="289">
@@ -8296,17 +8296,17 @@
       </c>
       <c r="C289" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D289" s="14" t="n">
-        <v>1357</v>
+        <v>3914</v>
       </c>
       <c r="E289" s="14" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="F289" s="15" t="n">
-        <v>15357805.31</v>
+        <v>33356940.44</v>
       </c>
     </row>
     <row r="290">
@@ -8322,17 +8322,17 @@
       </c>
       <c r="C290" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D290" s="10" t="n">
-        <v>213</v>
+        <v>1380</v>
       </c>
       <c r="E290" s="10" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F290" s="11" t="n">
-        <v>3230231.31</v>
+        <v>15671665.77</v>
       </c>
     </row>
     <row r="291">
@@ -8348,17 +8348,17 @@
       </c>
       <c r="C291" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D291" s="14" t="n">
-        <v>20</v>
+        <v>218</v>
       </c>
       <c r="E291" s="14" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F291" s="15" t="n">
-        <v>24353.84</v>
+        <v>3305943.1</v>
       </c>
     </row>
     <row r="292">
@@ -8369,22 +8369,22 @@
       </c>
       <c r="B292" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C292" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D292" s="10" t="n">
-        <v>584</v>
+        <v>20</v>
       </c>
       <c r="E292" s="10" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F292" s="11" t="n">
-        <v>8227282.46</v>
+        <v>24353.84</v>
       </c>
     </row>
     <row r="293">
@@ -8400,17 +8400,17 @@
       </c>
       <c r="C293" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D293" s="14" t="n">
-        <v>23</v>
+        <v>595</v>
       </c>
       <c r="E293" s="14" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F293" s="15" t="n">
-        <v>250691.88</v>
+        <v>8399285.560000001</v>
       </c>
     </row>
     <row r="294">
@@ -8426,17 +8426,17 @@
       </c>
       <c r="C294" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D294" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="E294" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E294" s="10" t="n">
-        <v>1</v>
-      </c>
       <c r="F294" s="11" t="n">
-        <v>27656.99</v>
+        <v>250691.88</v>
       </c>
     </row>
     <row r="295">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="B295" s="12" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C295" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D295" s="14" t="n">
@@ -8462,33 +8462,33 @@
         <v>1</v>
       </c>
       <c r="F295" s="15" t="n">
-        <v>39248.41</v>
+        <v>27656.99</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Recursos Humanos</t>
+          <t>Secretaria de Planejamento e Desenvolvimento Urbano</t>
         </is>
       </c>
       <c r="B296" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C296" s="9" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D296" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E296" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F296" s="11" t="n">
-        <v>6139.44</v>
+        <v>39248.41</v>
       </c>
     </row>
     <row r="297">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="B297" s="12" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C297" s="13" t="inlineStr">
@@ -8508,13 +8508,13 @@
         </is>
       </c>
       <c r="D297" s="14" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="E297" s="14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F297" s="15" t="n">
-        <v>30671.76</v>
+        <v>6139.44</v>
       </c>
     </row>
     <row r="298">
@@ -8525,22 +8525,22 @@
       </c>
       <c r="B298" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C298" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D298" s="10" t="n">
-        <v>1637</v>
+        <v>33</v>
       </c>
       <c r="E298" s="10" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="F298" s="11" t="n">
-        <v>7069207.91</v>
+        <v>30671.76</v>
       </c>
     </row>
     <row r="299">
@@ -8556,17 +8556,17 @@
       </c>
       <c r="C299" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D299" s="14" t="n">
-        <v>33</v>
+        <v>1675</v>
       </c>
       <c r="E299" s="14" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F299" s="15" t="n">
-        <v>286646.46</v>
+        <v>7266824.75</v>
       </c>
     </row>
     <row r="300">
@@ -8582,17 +8582,17 @@
       </c>
       <c r="C300" s="9" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D300" s="10" t="n">
-        <v>217</v>
+        <v>35</v>
       </c>
       <c r="E300" s="10" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="F300" s="11" t="n">
-        <v>218978.16</v>
+        <v>310708.4</v>
       </c>
     </row>
     <row r="301">
@@ -8603,22 +8603,22 @@
       </c>
       <c r="B301" s="12" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C301" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D301" s="14" t="n">
-        <v>102</v>
+        <v>217</v>
       </c>
       <c r="E301" s="14" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="F301" s="15" t="n">
-        <v>1188997.59</v>
+        <v>218978.16</v>
       </c>
     </row>
     <row r="302">
@@ -8634,17 +8634,17 @@
       </c>
       <c r="C302" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D302" s="10" t="n">
-        <v>151</v>
+        <v>104</v>
       </c>
       <c r="E302" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F302" s="11" t="n">
-        <v>888134.86</v>
+        <v>1206617.1</v>
       </c>
     </row>
     <row r="303">
@@ -8660,17 +8660,17 @@
       </c>
       <c r="C303" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D303" s="14" t="n">
-        <v>502</v>
+        <v>152</v>
       </c>
       <c r="E303" s="14" t="n">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="F303" s="15" t="n">
-        <v>500786.88</v>
+        <v>895922.3200000001</v>
       </c>
     </row>
     <row r="304">
@@ -8681,22 +8681,22 @@
       </c>
       <c r="B304" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C304" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D304" s="10" t="n">
-        <v>3107</v>
+        <v>513</v>
       </c>
       <c r="E304" s="10" t="n">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F304" s="11" t="n">
-        <v>21692579.76</v>
+        <v>511743.92</v>
       </c>
     </row>
     <row r="305">
@@ -8712,17 +8712,17 @@
       </c>
       <c r="C305" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D305" s="14" t="n">
-        <v>1150</v>
+        <v>3156</v>
       </c>
       <c r="E305" s="14" t="n">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="F305" s="15" t="n">
-        <v>12325812.36</v>
+        <v>22166400.76</v>
       </c>
     </row>
     <row r="306">
@@ -8738,17 +8738,17 @@
       </c>
       <c r="C306" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D306" s="10" t="n">
-        <v>80</v>
+        <v>1168</v>
       </c>
       <c r="E306" s="10" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F306" s="11" t="n">
-        <v>1081345.53</v>
+        <v>12626104.9</v>
       </c>
     </row>
     <row r="307">
@@ -8764,17 +8764,17 @@
       </c>
       <c r="C307" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D307" s="14" t="n">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="E307" s="14" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F307" s="15" t="n">
-        <v>15012.32</v>
+        <v>1096798.32</v>
       </c>
     </row>
     <row r="308">
@@ -8785,22 +8785,22 @@
       </c>
       <c r="B308" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C308" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D308" s="10" t="n">
-        <v>877</v>
+        <v>15</v>
       </c>
       <c r="E308" s="10" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F308" s="11" t="n">
-        <v>10312103.3</v>
+        <v>15012.32</v>
       </c>
     </row>
     <row r="309">
@@ -8816,17 +8816,17 @@
       </c>
       <c r="C309" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D309" s="14" t="n">
-        <v>303</v>
+        <v>890</v>
       </c>
       <c r="E309" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F309" s="15" t="n">
-        <v>2838397.57</v>
+        <v>10525550.42</v>
       </c>
     </row>
     <row r="310">
@@ -8842,17 +8842,17 @@
       </c>
       <c r="C310" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D310" s="10" t="n">
-        <v>60</v>
+        <v>305</v>
       </c>
       <c r="E310" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F310" s="11" t="n">
-        <v>1165660.55</v>
+        <v>2861483.01</v>
       </c>
     </row>
     <row r="311">
@@ -8863,48 +8863,48 @@
       </c>
       <c r="B311" s="12" t="inlineStr">
         <is>
-          <t>Doutorado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C311" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D311" s="14" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="E311" s="14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F311" s="15" t="n">
-        <v>687948.52</v>
+        <v>1188157.63</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Relações Institucionais e Metropolitanas</t>
+          <t>Secretaria de Recursos Humanos</t>
         </is>
       </c>
       <c r="B312" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Doutorado</t>
         </is>
       </c>
       <c r="C312" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D312" s="10" t="n">
-        <v>298</v>
+        <v>79</v>
       </c>
       <c r="E312" s="10" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F312" s="11" t="n">
-        <v>4234586.68</v>
+        <v>703389.36</v>
       </c>
     </row>
     <row r="313">
@@ -8920,17 +8920,17 @@
       </c>
       <c r="C313" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D313" s="14" t="n">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="E313" s="14" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F313" s="15" t="n">
-        <v>2839639.88</v>
+        <v>4234586.68</v>
       </c>
     </row>
     <row r="314">
@@ -8946,17 +8946,17 @@
       </c>
       <c r="C314" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D314" s="10" t="n">
-        <v>139</v>
+        <v>266</v>
       </c>
       <c r="E314" s="10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F314" s="11" t="n">
-        <v>1101856.17</v>
+        <v>2981165.73</v>
       </c>
     </row>
     <row r="315">
@@ -8967,22 +8967,22 @@
       </c>
       <c r="B315" s="12" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C315" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D315" s="14" t="n">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="E315" s="14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F315" s="15" t="n">
-        <v>877865.37</v>
+        <v>1107894.81</v>
       </c>
     </row>
     <row r="316">
@@ -8998,17 +8998,17 @@
       </c>
       <c r="C316" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D316" s="10" t="n">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="E316" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F316" s="11" t="n">
-        <v>236952.59</v>
+        <v>877865.37</v>
       </c>
     </row>
     <row r="317">
@@ -9024,43 +9024,43 @@
       </c>
       <c r="C317" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D317" s="14" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E317" s="14" t="n">
         <v>1</v>
       </c>
       <c r="F317" s="15" t="n">
-        <v>33953.56</v>
+        <v>248751.94</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Relações do Trabalho e Qualificação Profissional</t>
+          <t>Secretaria de Relações Institucionais e Metropolitanas</t>
         </is>
       </c>
       <c r="B318" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C318" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D318" s="10" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E318" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F318" s="11" t="n">
-        <v>116826.88</v>
+        <v>49406.35</v>
       </c>
     </row>
     <row r="319">
@@ -9071,22 +9071,22 @@
       </c>
       <c r="B319" s="12" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C319" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D319" s="14" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="E319" s="14" t="n">
         <v>1</v>
       </c>
       <c r="F319" s="15" t="n">
-        <v>2518.08</v>
+        <v>120539.78</v>
       </c>
     </row>
     <row r="320">
@@ -9097,22 +9097,22 @@
       </c>
       <c r="B320" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C320" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D320" s="10" t="n">
-        <v>302</v>
+        <v>3</v>
       </c>
       <c r="E320" s="10" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F320" s="11" t="n">
-        <v>1093484.53</v>
+        <v>2518.08</v>
       </c>
     </row>
     <row r="321">
@@ -9128,17 +9128,17 @@
       </c>
       <c r="C321" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D321" s="14" t="n">
-        <v>19</v>
+        <v>310</v>
       </c>
       <c r="E321" s="14" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F321" s="15" t="n">
-        <v>19062.24</v>
+        <v>1129232.2</v>
       </c>
     </row>
     <row r="322">
@@ -9149,22 +9149,22 @@
       </c>
       <c r="B322" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C322" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D322" s="10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E322" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F322" s="11" t="n">
-        <v>451812.29</v>
+        <v>19062.24</v>
       </c>
     </row>
     <row r="323">
@@ -9180,17 +9180,17 @@
       </c>
       <c r="C323" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D323" s="14" t="n">
-        <v>451</v>
+        <v>23</v>
       </c>
       <c r="E323" s="14" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="F323" s="15" t="n">
-        <v>443989.12</v>
+        <v>478058.83</v>
       </c>
     </row>
     <row r="324">
@@ -9201,22 +9201,22 @@
       </c>
       <c r="B324" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C324" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D324" s="10" t="n">
-        <v>556</v>
+        <v>456</v>
       </c>
       <c r="E324" s="10" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F324" s="11" t="n">
-        <v>4999745.67</v>
+        <v>449233.12</v>
       </c>
     </row>
     <row r="325">
@@ -9232,17 +9232,17 @@
       </c>
       <c r="C325" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D325" s="14" t="n">
-        <v>149</v>
+        <v>566</v>
       </c>
       <c r="E325" s="14" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F325" s="15" t="n">
-        <v>2365315.96</v>
+        <v>5100928.41</v>
       </c>
     </row>
     <row r="326">
@@ -9258,17 +9258,17 @@
       </c>
       <c r="C326" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D326" s="10" t="n">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="E326" s="10" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F326" s="11" t="n">
-        <v>1903824.87</v>
+        <v>2470902.69</v>
       </c>
     </row>
     <row r="327">
@@ -9279,22 +9279,22 @@
       </c>
       <c r="B327" s="12" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C327" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D327" s="14" t="n">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="E327" s="14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F327" s="15" t="n">
-        <v>314983.73</v>
+        <v>1946248.49</v>
       </c>
     </row>
     <row r="328">
@@ -9310,17 +9310,17 @@
       </c>
       <c r="C328" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D328" s="10" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E328" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F328" s="11" t="n">
-        <v>96705.67</v>
+        <v>314983.73</v>
       </c>
     </row>
     <row r="329">
@@ -9336,43 +9336,43 @@
       </c>
       <c r="C329" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D329" s="14" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E329" s="14" t="n">
         <v>1</v>
       </c>
       <c r="F329" s="15" t="n">
-        <v>34576.15</v>
+        <v>96705.67</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Segurança Urbana</t>
+          <t>Secretaria de Relações do Trabalho e Qualificação Profissional</t>
         </is>
       </c>
       <c r="B330" s="8" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C330" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D330" s="10" t="n">
-        <v>533</v>
+        <v>5</v>
       </c>
       <c r="E330" s="10" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F330" s="11" t="n">
-        <v>2741979.81</v>
+        <v>45534.21</v>
       </c>
     </row>
     <row r="331">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="B331" s="12" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C331" s="13" t="inlineStr">
@@ -9392,13 +9392,13 @@
         </is>
       </c>
       <c r="D331" s="14" t="n">
-        <v>757</v>
+        <v>537</v>
       </c>
       <c r="E331" s="14" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F331" s="15" t="n">
-        <v>6641436.89</v>
+        <v>2768656.32</v>
       </c>
     </row>
     <row r="332">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="B332" s="8" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C332" s="9" t="inlineStr">
@@ -9418,13 +9418,13 @@
         </is>
       </c>
       <c r="D332" s="10" t="n">
-        <v>462</v>
+        <v>763</v>
       </c>
       <c r="E332" s="10" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F332" s="11" t="n">
-        <v>4533182.09</v>
+        <v>6709546.52</v>
       </c>
     </row>
     <row r="333">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="B333" s="12" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C333" s="13" t="inlineStr">
@@ -9444,13 +9444,13 @@
         </is>
       </c>
       <c r="D333" s="14" t="n">
-        <v>15496</v>
+        <v>465</v>
       </c>
       <c r="E333" s="14" t="n">
-        <v>502</v>
+        <v>10</v>
       </c>
       <c r="F333" s="15" t="n">
-        <v>143775509.56</v>
+        <v>4569074.76</v>
       </c>
     </row>
     <row r="334">
@@ -9466,17 +9466,17 @@
       </c>
       <c r="C334" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D334" s="10" t="n">
-        <v>15</v>
+        <v>15932</v>
       </c>
       <c r="E334" s="10" t="n">
-        <v>2</v>
+        <v>502</v>
       </c>
       <c r="F334" s="11" t="n">
-        <v>206065.27</v>
+        <v>147748397.31</v>
       </c>
     </row>
     <row r="335">
@@ -9492,17 +9492,17 @@
       </c>
       <c r="C335" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D335" s="14" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E335" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F335" s="15" t="n">
-        <v>31691.2</v>
+        <v>214679.18</v>
       </c>
     </row>
     <row r="336">
@@ -9513,22 +9513,22 @@
       </c>
       <c r="B336" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C336" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D336" s="10" t="n">
-        <v>947</v>
+        <v>30</v>
       </c>
       <c r="E336" s="10" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F336" s="11" t="n">
-        <v>8259281.19</v>
+        <v>31691.2</v>
       </c>
     </row>
     <row r="337">
@@ -9544,17 +9544,17 @@
       </c>
       <c r="C337" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D337" s="14" t="n">
-        <v>788</v>
+        <v>958</v>
       </c>
       <c r="E337" s="14" t="n">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="F337" s="15" t="n">
-        <v>821107.84</v>
+        <v>8394302.07</v>
       </c>
     </row>
     <row r="338">
@@ -9570,17 +9570,17 @@
       </c>
       <c r="C338" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D338" s="10" t="n">
-        <v>31</v>
+        <v>813</v>
       </c>
       <c r="E338" s="10" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="F338" s="11" t="n">
-        <v>245051.49</v>
+        <v>847921.4399999999</v>
       </c>
     </row>
     <row r="339">
@@ -9596,17 +9596,17 @@
       </c>
       <c r="C339" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D339" s="14" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E339" s="14" t="n">
         <v>1</v>
       </c>
       <c r="F339" s="15" t="n">
-        <v>58539.94</v>
+        <v>245051.49</v>
       </c>
     </row>
     <row r="340">
@@ -9617,22 +9617,22 @@
       </c>
       <c r="B340" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C340" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D340" s="10" t="n">
-        <v>7300</v>
+        <v>4</v>
       </c>
       <c r="E340" s="10" t="n">
-        <v>142</v>
+        <v>1</v>
       </c>
       <c r="F340" s="11" t="n">
-        <v>82804231.41</v>
+        <v>58539.94</v>
       </c>
     </row>
     <row r="341">
@@ -9648,17 +9648,17 @@
       </c>
       <c r="C341" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D341" s="14" t="n">
-        <v>879</v>
+        <v>7404</v>
       </c>
       <c r="E341" s="14" t="n">
-        <v>25</v>
+        <v>142</v>
       </c>
       <c r="F341" s="15" t="n">
-        <v>12609021.88</v>
+        <v>84379627.27</v>
       </c>
     </row>
     <row r="342">
@@ -9674,17 +9674,17 @@
       </c>
       <c r="C342" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D342" s="10" t="n">
-        <v>192</v>
+        <v>891</v>
       </c>
       <c r="E342" s="10" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F342" s="11" t="n">
-        <v>2968837.11</v>
+        <v>12816672.36</v>
       </c>
     </row>
     <row r="343">
@@ -9695,22 +9695,22 @@
       </c>
       <c r="B343" s="12" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C343" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D343" s="14" t="n">
-        <v>425</v>
+        <v>194</v>
       </c>
       <c r="E343" s="14" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F343" s="15" t="n">
-        <v>7037037.23</v>
+        <v>2995823.03</v>
       </c>
     </row>
     <row r="344">
@@ -9726,17 +9726,17 @@
       </c>
       <c r="C344" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D344" s="10" t="n">
-        <v>90</v>
+        <v>430</v>
       </c>
       <c r="E344" s="10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F344" s="11" t="n">
-        <v>1937947.5</v>
+        <v>7164120.94</v>
       </c>
     </row>
     <row r="345">
@@ -9752,17 +9752,17 @@
       </c>
       <c r="C345" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D345" s="14" t="n">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="E345" s="14" t="n">
         <v>2</v>
       </c>
       <c r="F345" s="15" t="n">
-        <v>400310.83</v>
+        <v>1992846.24</v>
       </c>
     </row>
     <row r="346">
@@ -9773,33 +9773,33 @@
       </c>
       <c r="B346" s="8" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C346" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D346" s="10" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E346" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F346" s="11" t="n">
-        <v>459565.73</v>
+        <v>400310.83</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Serviços Públicos e Obras</t>
+          <t>Secretaria de Segurança Urbana</t>
         </is>
       </c>
       <c r="B347" s="12" t="inlineStr">
         <is>
-          <t>Sem escolaridade formal registrada</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C347" s="13" t="inlineStr">
@@ -9808,13 +9808,13 @@
         </is>
       </c>
       <c r="D347" s="14" t="n">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="E347" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F347" s="15" t="n">
-        <v>509725.96</v>
+        <v>459565.73</v>
       </c>
     </row>
     <row r="348">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="B348" s="8" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Sem escolaridade formal registrada</t>
         </is>
       </c>
       <c r="C348" s="9" t="inlineStr">
@@ -9834,13 +9834,13 @@
         </is>
       </c>
       <c r="D348" s="10" t="n">
-        <v>584</v>
+        <v>105</v>
       </c>
       <c r="E348" s="10" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F348" s="11" t="n">
-        <v>3675419.78</v>
+        <v>516033.54</v>
       </c>
     </row>
     <row r="349">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="B349" s="12" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C349" s="13" t="inlineStr">
@@ -9860,13 +9860,13 @@
         </is>
       </c>
       <c r="D349" s="14" t="n">
-        <v>785</v>
+        <v>591</v>
       </c>
       <c r="E349" s="14" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F349" s="15" t="n">
-        <v>3563494.45</v>
+        <v>3731997.35</v>
       </c>
     </row>
     <row r="350">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="B350" s="8" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C350" s="9" t="inlineStr">
@@ -9886,13 +9886,13 @@
         </is>
       </c>
       <c r="D350" s="10" t="n">
-        <v>79</v>
+        <v>804</v>
       </c>
       <c r="E350" s="10" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F350" s="11" t="n">
-        <v>267256.97</v>
+        <v>3657534.78</v>
       </c>
     </row>
     <row r="351">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="B351" s="12" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C351" s="13" t="inlineStr">
@@ -9912,13 +9912,13 @@
         </is>
       </c>
       <c r="D351" s="14" t="n">
-        <v>2685</v>
+        <v>80</v>
       </c>
       <c r="E351" s="14" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="F351" s="15" t="n">
-        <v>11246765.86</v>
+        <v>271481.51</v>
       </c>
     </row>
     <row r="352">
@@ -9934,17 +9934,17 @@
       </c>
       <c r="C352" s="9" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D352" s="10" t="n">
-        <v>13</v>
+        <v>2731</v>
       </c>
       <c r="E352" s="10" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="F352" s="11" t="n">
-        <v>13519.84</v>
+        <v>11519058.96</v>
       </c>
     </row>
     <row r="353">
@@ -9955,22 +9955,22 @@
       </c>
       <c r="B353" s="12" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C353" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D353" s="14" t="n">
-        <v>333</v>
+        <v>13</v>
       </c>
       <c r="E353" s="14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F353" s="15" t="n">
-        <v>1947914.02</v>
+        <v>13519.84</v>
       </c>
     </row>
     <row r="354">
@@ -9986,17 +9986,17 @@
       </c>
       <c r="C354" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D354" s="10" t="n">
-        <v>62</v>
+        <v>337</v>
       </c>
       <c r="E354" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F354" s="11" t="n">
-        <v>596041.29</v>
+        <v>1977138.65</v>
       </c>
     </row>
     <row r="355">
@@ -10012,17 +10012,17 @@
       </c>
       <c r="C355" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D355" s="14" t="n">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="E355" s="14" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F355" s="15" t="n">
-        <v>117955.44</v>
+        <v>607372.25</v>
       </c>
     </row>
     <row r="356">
@@ -10033,22 +10033,22 @@
       </c>
       <c r="B356" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C356" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D356" s="10" t="n">
-        <v>2720</v>
+        <v>116</v>
       </c>
       <c r="E356" s="10" t="n">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="F356" s="11" t="n">
-        <v>25759034.63</v>
+        <v>117955.44</v>
       </c>
     </row>
     <row r="357">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="C357" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D357" s="14" t="n">
-        <v>1250</v>
+        <v>2761</v>
       </c>
       <c r="E357" s="14" t="n">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="F357" s="15" t="n">
-        <v>13003394.73</v>
+        <v>26201672.32</v>
       </c>
     </row>
     <row r="358">
@@ -10090,17 +10090,17 @@
       </c>
       <c r="C358" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D358" s="10" t="n">
-        <v>643</v>
+        <v>1270</v>
       </c>
       <c r="E358" s="10" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F358" s="11" t="n">
-        <v>8968143.6</v>
+        <v>13276042.53</v>
       </c>
     </row>
     <row r="359">
@@ -10111,22 +10111,22 @@
       </c>
       <c r="B359" s="12" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C359" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D359" s="14" t="n">
-        <v>379</v>
+        <v>659</v>
       </c>
       <c r="E359" s="14" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="F359" s="15" t="n">
-        <v>4858078.31</v>
+        <v>9212059.040000001</v>
       </c>
     </row>
     <row r="360">
@@ -10142,17 +10142,17 @@
       </c>
       <c r="C360" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D360" s="10" t="n">
-        <v>74</v>
+        <v>385</v>
       </c>
       <c r="E360" s="10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F360" s="11" t="n">
-        <v>836493.25</v>
+        <v>5004976.22</v>
       </c>
     </row>
     <row r="361">
@@ -10168,17 +10168,17 @@
       </c>
       <c r="C361" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D361" s="14" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="E361" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F361" s="15" t="n">
-        <v>93426.24000000001</v>
+        <v>852215.55</v>
       </c>
     </row>
     <row r="362">
@@ -10189,22 +10189,22 @@
       </c>
       <c r="B362" s="8" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C362" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D362" s="10" t="n">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="E362" s="10" t="n">
         <v>2</v>
       </c>
       <c r="F362" s="11" t="n">
-        <v>776835.8200000001</v>
+        <v>93426.24000000001</v>
       </c>
     </row>
     <row r="363">
@@ -10220,17 +10220,17 @@
       </c>
       <c r="C363" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D363" s="14" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="E363" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F363" s="15" t="n">
-        <v>374789.37</v>
+        <v>794424.86</v>
       </c>
     </row>
     <row r="364">
@@ -10246,43 +10246,43 @@
       </c>
       <c r="C364" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D364" s="10" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E364" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F364" s="11" t="n">
-        <v>29278.76</v>
+        <v>374789.37</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Turismo</t>
+          <t>Secretaria de Serviços Públicos e Obras</t>
         </is>
       </c>
       <c r="B365" s="12" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C365" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D365" s="14" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="E365" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F365" s="15" t="n">
-        <v>148995.2</v>
+        <v>29278.76</v>
       </c>
     </row>
     <row r="366">
@@ -10293,22 +10293,22 @@
       </c>
       <c r="B366" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C366" s="9" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D366" s="10" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E366" s="10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F366" s="11" t="n">
-        <v>39391.92</v>
+        <v>158547.56</v>
       </c>
     </row>
     <row r="367">
@@ -10319,22 +10319,22 @@
       </c>
       <c r="B367" s="12" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C367" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D367" s="14" t="n">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="E367" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F367" s="15" t="n">
-        <v>1598836.67</v>
+        <v>44146.32</v>
       </c>
     </row>
     <row r="368">
@@ -10350,17 +10350,17 @@
       </c>
       <c r="C368" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D368" s="10" t="n">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="E368" s="10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F368" s="11" t="n">
-        <v>527318.99</v>
+        <v>1684987.77</v>
       </c>
     </row>
     <row r="369">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="C369" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D369" s="14" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="E369" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F369" s="15" t="n">
-        <v>241748.51</v>
+        <v>551702.48</v>
       </c>
     </row>
     <row r="370">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="B370" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C370" s="9" t="inlineStr">
@@ -10406,13 +10406,13 @@
         </is>
       </c>
       <c r="D370" s="10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E370" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F370" s="11" t="n">
-        <v>296779.43</v>
+        <v>252158.58</v>
       </c>
     </row>
     <row r="371">
@@ -10428,17 +10428,17 @@
       </c>
       <c r="C371" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D371" s="14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E371" s="14" t="n">
         <v>1</v>
       </c>
       <c r="F371" s="15" t="n">
-        <v>231606.21</v>
+        <v>311710.33</v>
       </c>
     </row>
     <row r="372">
@@ -10454,43 +10454,43 @@
       </c>
       <c r="C372" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D372" s="10" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E372" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F372" s="11" t="n">
-        <v>21293.36</v>
+        <v>244274.98</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Urbanismo e Licenciamento</t>
+          <t>Secretaria de Turismo</t>
         </is>
       </c>
       <c r="B373" s="12" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C373" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D373" s="14" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E373" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F373" s="15" t="n">
-        <v>110940.25</v>
+        <v>21293.36</v>
       </c>
     </row>
     <row r="374">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="B374" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C374" s="9" t="inlineStr">
@@ -10510,13 +10510,13 @@
         </is>
       </c>
       <c r="D374" s="10" t="n">
-        <v>487</v>
+        <v>30</v>
       </c>
       <c r="E374" s="10" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="F374" s="11" t="n">
-        <v>2465567.23</v>
+        <v>110940.25</v>
       </c>
     </row>
     <row r="375">
@@ -10527,22 +10527,22 @@
       </c>
       <c r="B375" s="12" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C375" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D375" s="14" t="n">
-        <v>323</v>
+        <v>487</v>
       </c>
       <c r="E375" s="14" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="F375" s="15" t="n">
-        <v>343541.47</v>
+        <v>2465567.23</v>
       </c>
     </row>
     <row r="376">
@@ -10558,17 +10558,17 @@
       </c>
       <c r="C376" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D376" s="10" t="n">
-        <v>47</v>
+        <v>323</v>
       </c>
       <c r="E376" s="10" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="F376" s="11" t="n">
-        <v>156850.26</v>
+        <v>343541.47</v>
       </c>
     </row>
     <row r="377">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="B377" s="12" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C377" s="13" t="inlineStr">
@@ -10588,13 +10588,13 @@
         </is>
       </c>
       <c r="D377" s="14" t="n">
-        <v>992</v>
+        <v>47</v>
       </c>
       <c r="E377" s="14" t="n">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="F377" s="15" t="n">
-        <v>6779742.41</v>
+        <v>156850.26</v>
       </c>
     </row>
     <row r="378">
@@ -10610,17 +10610,17 @@
       </c>
       <c r="C378" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D378" s="10" t="n">
-        <v>317</v>
+        <v>992</v>
       </c>
       <c r="E378" s="10" t="n">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="F378" s="11" t="n">
-        <v>2855746.37</v>
+        <v>6779742.41</v>
       </c>
     </row>
     <row r="379">
@@ -10636,17 +10636,17 @@
       </c>
       <c r="C379" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D379" s="14" t="n">
-        <v>53</v>
+        <v>317</v>
       </c>
       <c r="E379" s="14" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="F379" s="15" t="n">
-        <v>697610.13</v>
+        <v>2855746.37</v>
       </c>
     </row>
     <row r="380">
@@ -10662,17 +10662,17 @@
       </c>
       <c r="C380" s="9" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D380" s="10" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E380" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F380" s="11" t="n">
-        <v>39296.56</v>
+        <v>697610.13</v>
       </c>
     </row>
     <row r="381">
@@ -10683,22 +10683,22 @@
       </c>
       <c r="B381" s="12" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C381" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D381" s="14" t="n">
-        <v>136</v>
+        <v>38</v>
       </c>
       <c r="E381" s="14" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F381" s="15" t="n">
-        <v>1787840.82</v>
+        <v>39296.56</v>
       </c>
     </row>
     <row r="382">
@@ -10714,17 +10714,17 @@
       </c>
       <c r="C382" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D382" s="10" t="n">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="E382" s="10" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F382" s="11" t="n">
-        <v>187892.95</v>
+        <v>1787840.82</v>
       </c>
     </row>
     <row r="383">
@@ -10735,22 +10735,22 @@
       </c>
       <c r="B383" s="12" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C383" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D383" s="14" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E383" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F383" s="15" t="n">
-        <v>145945.63</v>
+        <v>187892.95</v>
       </c>
     </row>
     <row r="384">
@@ -10761,7 +10761,7 @@
       </c>
       <c r="B384" s="8" t="inlineStr">
         <is>
-          <t>Doutorado</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C384" s="9" t="inlineStr">
@@ -10770,24 +10770,24 @@
         </is>
       </c>
       <c r="D384" s="10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E384" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F384" s="11" t="n">
-        <v>49067.89</v>
+        <v>145945.63</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="12" t="inlineStr">
         <is>
-          <t>Secretaria do Meio Ambiente, Parques e Jardins</t>
+          <t>Secretaria de Urbanismo e Licenciamento</t>
         </is>
       </c>
       <c r="B385" s="12" t="inlineStr">
         <is>
-          <t>Sem escolaridade formal registrada</t>
+          <t>Doutorado</t>
         </is>
       </c>
       <c r="C385" s="13" t="inlineStr">
@@ -10796,13 +10796,13 @@
         </is>
       </c>
       <c r="D385" s="14" t="n">
-        <v>122</v>
+        <v>3</v>
       </c>
       <c r="E385" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F385" s="15" t="n">
-        <v>685031.04</v>
+        <v>49067.89</v>
       </c>
     </row>
     <row r="386">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="B386" s="8" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Sem escolaridade formal registrada</t>
         </is>
       </c>
       <c r="C386" s="9" t="inlineStr">
@@ -10822,13 +10822,13 @@
         </is>
       </c>
       <c r="D386" s="10" t="n">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E386" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F386" s="11" t="n">
-        <v>763943.79</v>
+        <v>685031.04</v>
       </c>
     </row>
     <row r="387">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="B387" s="12" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C387" s="13" t="inlineStr">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="D387" s="14" t="n">
-        <v>282</v>
+        <v>140</v>
       </c>
       <c r="E387" s="14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F387" s="15" t="n">
-        <v>1424403.14</v>
+        <v>780440.42</v>
       </c>
     </row>
     <row r="388">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="B388" s="8" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C388" s="9" t="inlineStr">
@@ -10874,13 +10874,13 @@
         </is>
       </c>
       <c r="D388" s="10" t="n">
-        <v>25</v>
+        <v>288</v>
       </c>
       <c r="E388" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F388" s="11" t="n">
-        <v>188335.02</v>
+        <v>1447220.35</v>
       </c>
     </row>
     <row r="389">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="B389" s="12" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C389" s="13" t="inlineStr">
@@ -10900,13 +10900,13 @@
         </is>
       </c>
       <c r="D389" s="14" t="n">
-        <v>778</v>
+        <v>25</v>
       </c>
       <c r="E389" s="14" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="F389" s="15" t="n">
-        <v>4088446.27</v>
+        <v>188335.02</v>
       </c>
     </row>
     <row r="390">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="C390" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D390" s="10" t="n">
-        <v>23</v>
+        <v>800</v>
       </c>
       <c r="E390" s="10" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F390" s="11" t="n">
-        <v>179730.54</v>
+        <v>4209485.93</v>
       </c>
     </row>
     <row r="391">
@@ -10943,22 +10943,22 @@
       </c>
       <c r="B391" s="12" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C391" s="13" t="inlineStr">
         <is>
-          <t>flexiveis</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D391" s="14" t="n">
-        <v>1063</v>
+        <v>25</v>
       </c>
       <c r="E391" s="14" t="n">
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="F391" s="15" t="n">
-        <v>1078975.64</v>
+        <v>198859.23</v>
       </c>
     </row>
     <row r="392">
@@ -10974,17 +10974,17 @@
       </c>
       <c r="C392" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>flexiveis</t>
         </is>
       </c>
       <c r="D392" s="10" t="n">
-        <v>200</v>
+        <v>1080</v>
       </c>
       <c r="E392" s="10" t="n">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="F392" s="11" t="n">
-        <v>731940.8</v>
+        <v>1094470.36</v>
       </c>
     </row>
     <row r="393">
@@ -11000,17 +11000,17 @@
       </c>
       <c r="C393" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D393" s="14" t="n">
-        <v>76</v>
+        <v>203</v>
       </c>
       <c r="E393" s="14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F393" s="15" t="n">
-        <v>573676.4</v>
+        <v>745667.89</v>
       </c>
     </row>
     <row r="394">
@@ -11021,22 +11021,22 @@
       </c>
       <c r="B394" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C394" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D394" s="10" t="n">
-        <v>2846</v>
+        <v>76</v>
       </c>
       <c r="E394" s="10" t="n">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="F394" s="11" t="n">
-        <v>27294521.61</v>
+        <v>573676.4</v>
       </c>
     </row>
     <row r="395">
@@ -11052,17 +11052,17 @@
       </c>
       <c r="C395" s="13" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D395" s="14" t="n">
-        <v>1203</v>
+        <v>2916</v>
       </c>
       <c r="E395" s="14" t="n">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="F395" s="15" t="n">
-        <v>12627772.79</v>
+        <v>27978712.34</v>
       </c>
     </row>
     <row r="396">
@@ -11078,17 +11078,17 @@
       </c>
       <c r="C396" s="9" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D396" s="10" t="n">
-        <v>279</v>
+        <v>1229</v>
       </c>
       <c r="E396" s="10" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F396" s="11" t="n">
-        <v>3968806.92</v>
+        <v>12913953.74</v>
       </c>
     </row>
     <row r="397">
@@ -11099,22 +11099,22 @@
       </c>
       <c r="B397" s="12" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C397" s="13" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D397" s="14" t="n">
-        <v>249</v>
+        <v>282</v>
       </c>
       <c r="E397" s="14" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="F397" s="15" t="n">
-        <v>2049980.08</v>
+        <v>4015165.29</v>
       </c>
     </row>
     <row r="398">
@@ -11130,17 +11130,17 @@
       </c>
       <c r="C398" s="9" t="inlineStr">
         <is>
-          <t>funcao_confianca</t>
+          <t>efetivos</t>
         </is>
       </c>
       <c r="D398" s="10" t="n">
-        <v>122</v>
+        <v>255</v>
       </c>
       <c r="E398" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F398" s="11" t="n">
-        <v>1089009.6</v>
+        <v>2102540.33</v>
       </c>
     </row>
     <row r="399">
@@ -11156,17 +11156,17 @@
       </c>
       <c r="C399" s="13" t="inlineStr">
         <is>
-          <t>comissionados</t>
+          <t>funcao_confianca</t>
         </is>
       </c>
       <c r="D399" s="14" t="n">
-        <v>10</v>
+        <v>124</v>
       </c>
       <c r="E399" s="14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F399" s="15" t="n">
-        <v>167534.56</v>
+        <v>1103022.28</v>
       </c>
     </row>
     <row r="400">
@@ -11177,22 +11177,22 @@
       </c>
       <c r="B400" s="8" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C400" s="9" t="inlineStr">
         <is>
-          <t>efetivos</t>
+          <t>comissionados</t>
         </is>
       </c>
       <c r="D400" s="10" t="n">
-        <v>226</v>
+        <v>10</v>
       </c>
       <c r="E400" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F400" s="11" t="n">
-        <v>1962245.74</v>
+        <v>167534.56</v>
       </c>
     </row>
     <row r="401">
@@ -11203,26 +11203,52 @@
       </c>
       <c r="B401" s="12" t="inlineStr">
         <is>
+          <t>Mestrado</t>
+        </is>
+      </c>
+      <c r="C401" s="13" t="inlineStr">
+        <is>
+          <t>efetivos</t>
+        </is>
+      </c>
+      <c r="D401" s="14" t="n">
+        <v>230</v>
+      </c>
+      <c r="E401" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F401" s="15" t="n">
+        <v>2007331</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="8" t="inlineStr">
+        <is>
+          <t>Secretaria do Meio Ambiente, Parques e Jardins</t>
+        </is>
+      </c>
+      <c r="B402" s="8" t="inlineStr">
+        <is>
           <t>Doutorado</t>
         </is>
       </c>
-      <c r="C401" s="13" t="inlineStr">
-        <is>
-          <t>efetivos</t>
-        </is>
-      </c>
-      <c r="D401" s="14" t="n">
-        <v>146</v>
-      </c>
-      <c r="E401" s="14" t="n">
+      <c r="C402" s="9" t="inlineStr">
+        <is>
+          <t>efetivos</t>
+        </is>
+      </c>
+      <c r="D402" s="10" t="n">
+        <v>148</v>
+      </c>
+      <c r="E402" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F401" s="15" t="n">
-        <v>1904545.53</v>
+      <c r="F402" s="11" t="n">
+        <v>1955464.99</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F401"/>
+  <autoFilter ref="A1:F402"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>